--- a/Grids Germany/No leap years/Saxony insights/[Saxony][Manhattan][CI]Yearly_U_test.xlsx
+++ b/Grids Germany/No leap years/Saxony insights/[Saxony][Manhattan][CI]Yearly_U_test.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,62 +429,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>YEAR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>mean_P1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>sd_P1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>mean_P2</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>sd_P2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>U_statistic</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>p_Bonferroni</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Significant</t>
         </is>
@@ -488,28 +500,28 @@
         <v>1996</v>
       </c>
       <c r="C2" t="n">
-        <v>8.345246796964432</v>
+        <v>8.598254928517669</v>
       </c>
       <c r="D2" t="n">
-        <v>5.309623712120739</v>
+        <v>5.141346990151886</v>
       </c>
       <c r="E2" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F2" t="n">
-        <v>9.77588932372457</v>
+        <v>9.802805258846968</v>
       </c>
       <c r="G2" t="n">
-        <v>2.308167304364144</v>
+        <v>2.376614740637278</v>
       </c>
       <c r="H2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I2" t="n">
-        <v>399</v>
+        <v>370</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4227178469296483</v>
+        <v>0.510645295808696</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -528,28 +540,28 @@
         <v>1997</v>
       </c>
       <c r="C3" t="n">
-        <v>8.916878852840982</v>
+        <v>9.05617235272101</v>
       </c>
       <c r="D3" t="n">
-        <v>5.860891907080179</v>
+        <v>5.847752545406935</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F3" t="n">
-        <v>10.79242588192136</v>
+        <v>10.68081946353742</v>
       </c>
       <c r="G3" t="n">
-        <v>2.067286641826799</v>
+        <v>2.080631349753332</v>
       </c>
       <c r="H3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="J3" t="n">
-        <v>0.09083445835238046</v>
+        <v>0.1271828834173821</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -568,28 +580,28 @@
         <v>1998</v>
       </c>
       <c r="C4" t="n">
-        <v>11.26132995888616</v>
+        <v>11.29433989520597</v>
       </c>
       <c r="D4" t="n">
-        <v>3.995057166762645</v>
+        <v>4.072428034830985</v>
       </c>
       <c r="E4" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F4" t="n">
-        <v>10.40134125747076</v>
+        <v>10.63545545559619</v>
       </c>
       <c r="G4" t="n">
-        <v>2.967992424238915</v>
+        <v>2.903063801873675</v>
       </c>
       <c r="H4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>494</v>
+        <v>441</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6420317542764774</v>
+        <v>0.7231755930051522</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -608,31 +620,31 @@
         <v>1999</v>
       </c>
       <c r="C5" t="n">
-        <v>9.941463697461794</v>
+        <v>10.02350372776129</v>
       </c>
       <c r="D5" t="n">
-        <v>3.163800100535086</v>
+        <v>3.067645645386634</v>
       </c>
       <c r="E5" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F5" t="n">
-        <v>15.18767356500527</v>
+        <v>15.60318521136043</v>
       </c>
       <c r="G5" t="n">
-        <v>2.695482743823109</v>
+        <v>2.187391172898351</v>
       </c>
       <c r="H5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="J5" t="n">
-        <v>1.272666963835917e-06</v>
+        <v>2.546727203695005e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>3.818000891507751e-05</v>
+        <v>7.640181611085013e-06</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -648,28 +660,28 @@
         <v>2000</v>
       </c>
       <c r="C6" t="n">
-        <v>12.33007390036812</v>
+        <v>12.56808528478833</v>
       </c>
       <c r="D6" t="n">
-        <v>5.248847592092015</v>
+        <v>5.169332998944463</v>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F6" t="n">
-        <v>12.64488869034344</v>
+        <v>12.52955214127</v>
       </c>
       <c r="G6" t="n">
-        <v>2.704926389223146</v>
+        <v>2.747321079146667</v>
       </c>
       <c r="H6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>468</v>
+        <v>445</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9088171020576624</v>
+        <v>0.6803032233889605</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -688,31 +700,31 @@
         <v>2001</v>
       </c>
       <c r="C7" t="n">
-        <v>9.501916653634034</v>
+        <v>9.699387479166678</v>
       </c>
       <c r="D7" t="n">
-        <v>4.885445187069585</v>
+        <v>4.866955905592094</v>
       </c>
       <c r="E7" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F7" t="n">
-        <v>12.32608805538639</v>
+        <v>12.4223187575424</v>
       </c>
       <c r="G7" t="n">
-        <v>2.553800544408426</v>
+        <v>2.602323938381447</v>
       </c>
       <c r="H7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>299</v>
+        <v>276</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03162369035229476</v>
+        <v>0.04370873442411537</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9487107105688428</v>
+        <v>1</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
@@ -728,28 +740,28 @@
         <v>2002</v>
       </c>
       <c r="C8" t="n">
-        <v>10.26426294643038</v>
+        <v>10.42073328925828</v>
       </c>
       <c r="D8" t="n">
-        <v>4.414152004003384</v>
+        <v>4.516253496423597</v>
       </c>
       <c r="E8" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F8" t="n">
-        <v>10.06235009317105</v>
+        <v>10.02857516028101</v>
       </c>
       <c r="G8" t="n">
-        <v>1.899339875886108</v>
+        <v>1.952835765836415</v>
       </c>
       <c r="H8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9409243640314168</v>
+        <v>0.7779983132405091</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -768,28 +780,28 @@
         <v>2003</v>
       </c>
       <c r="C9" t="n">
-        <v>10.09376716889119</v>
+        <v>10.15835204400254</v>
       </c>
       <c r="D9" t="n">
-        <v>5.415352256225019</v>
+        <v>5.52203421805503</v>
       </c>
       <c r="E9" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F9" t="n">
-        <v>13.5011068897912</v>
+        <v>13.91372858783381</v>
       </c>
       <c r="G9" t="n">
-        <v>4.035784780960137</v>
+        <v>3.796204407865078</v>
       </c>
       <c r="H9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>318</v>
+        <v>279</v>
       </c>
       <c r="J9" t="n">
-        <v>0.05834120897946931</v>
+        <v>0.04843865810220309</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -808,28 +820,28 @@
         <v>2004</v>
       </c>
       <c r="C10" t="n">
-        <v>10.02829048976263</v>
+        <v>10.12881846583028</v>
       </c>
       <c r="D10" t="n">
-        <v>3.192232956932116</v>
+        <v>3.181472614787823</v>
       </c>
       <c r="E10" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F10" t="n">
-        <v>11.76781467265591</v>
+        <v>11.39355464548741</v>
       </c>
       <c r="G10" t="n">
-        <v>2.424100870415367</v>
+        <v>1.965281643786841</v>
       </c>
       <c r="H10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="J10" t="n">
-        <v>0.06201662086315939</v>
+        <v>0.1462192376549335</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -848,31 +860,31 @@
         <v>2005</v>
       </c>
       <c r="C11" t="n">
-        <v>9.509242834293737</v>
+        <v>9.60507204476659</v>
       </c>
       <c r="D11" t="n">
-        <v>3.686470573806325</v>
+        <v>3.717687041825108</v>
       </c>
       <c r="E11" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F11" t="n">
-        <v>11.5148026898586</v>
+        <v>11.41724968216667</v>
       </c>
       <c r="G11" t="n">
-        <v>2.157909156328562</v>
+        <v>2.187653001309039</v>
       </c>
       <c r="H11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I11" t="n">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="J11" t="n">
-        <v>0.01393084148473056</v>
+        <v>0.03296278268105365</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4179252445419167</v>
+        <v>0.9888834804316095</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
@@ -888,31 +900,31 @@
         <v>2006</v>
       </c>
       <c r="C12" t="n">
-        <v>10.28905501006237</v>
+        <v>10.45177277723393</v>
       </c>
       <c r="D12" t="n">
-        <v>3.818751177699265</v>
+        <v>3.929192621355224</v>
       </c>
       <c r="E12" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F12" t="n">
-        <v>15.40393104714648</v>
+        <v>15.70822987514651</v>
       </c>
       <c r="G12" t="n">
-        <v>1.899778701699956</v>
+        <v>1.503518990857801</v>
       </c>
       <c r="H12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="J12" t="n">
-        <v>4.509467784624938e-07</v>
+        <v>4.690257144171609e-07</v>
       </c>
       <c r="K12" t="n">
-        <v>1.352840335387481e-05</v>
+        <v>1.407077143251483e-05</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -928,28 +940,28 @@
         <v>2007</v>
       </c>
       <c r="C13" t="n">
-        <v>11.49808155080573</v>
+        <v>11.62588038443973</v>
       </c>
       <c r="D13" t="n">
-        <v>3.867606140576919</v>
+        <v>3.79909515769018</v>
       </c>
       <c r="E13" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F13" t="n">
-        <v>11.98461625012712</v>
+        <v>12.01023826452272</v>
       </c>
       <c r="G13" t="n">
-        <v>1.804717036864704</v>
+        <v>1.857257660511291</v>
       </c>
       <c r="H13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I13" t="n">
-        <v>407</v>
+        <v>383</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4877315200834065</v>
+        <v>0.6384401237208024</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -968,28 +980,28 @@
         <v>2008</v>
       </c>
       <c r="C14" t="n">
-        <v>9.601426281854833</v>
+        <v>9.684130484794894</v>
       </c>
       <c r="D14" t="n">
-        <v>3.683561732812322</v>
+        <v>3.734939134244192</v>
       </c>
       <c r="E14" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F14" t="n">
-        <v>9.324383327483039</v>
+        <v>9.3375035277755</v>
       </c>
       <c r="G14" t="n">
-        <v>1.113204905420918</v>
+        <v>1.146189495631886</v>
       </c>
       <c r="H14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I14" t="n">
-        <v>513</v>
+        <v>476</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4709896409740194</v>
+        <v>0.3896548518002457</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -1008,28 +1020,28 @@
         <v>2009</v>
       </c>
       <c r="C15" t="n">
-        <v>12.09554123745179</v>
+        <v>12.25955644863423</v>
       </c>
       <c r="D15" t="n">
-        <v>3.046815496670704</v>
+        <v>2.650375361754429</v>
       </c>
       <c r="E15" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F15" t="n">
-        <v>13.04376000147799</v>
+        <v>13.23434266630266</v>
       </c>
       <c r="G15" t="n">
-        <v>2.39147673063262</v>
+        <v>2.3364799863237</v>
       </c>
       <c r="H15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I15" t="n">
-        <v>386</v>
+        <v>334</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3286287619001479</v>
+        <v>0.2386703829252536</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1048,31 +1060,31 @@
         <v>2010</v>
       </c>
       <c r="C16" t="n">
-        <v>8.802317958100328</v>
+        <v>8.780264089930585</v>
       </c>
       <c r="D16" t="n">
-        <v>2.926596390860323</v>
+        <v>3.003801504340334</v>
       </c>
       <c r="E16" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F16" t="n">
-        <v>10.86677111884636</v>
+        <v>10.78088046047411</v>
       </c>
       <c r="G16" t="n">
-        <v>2.577756846355775</v>
+        <v>2.633385609446885</v>
       </c>
       <c r="H16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I16" t="n">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01243812101638054</v>
+        <v>0.02031445742460202</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3731436304914164</v>
+        <v>0.6094337227380606</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
@@ -1088,31 +1100,31 @@
         <v>2011</v>
       </c>
       <c r="C17" t="n">
-        <v>11.44268091783644</v>
+        <v>11.63128489380408</v>
       </c>
       <c r="D17" t="n">
-        <v>3.646284124054877</v>
+        <v>3.673289226154721</v>
       </c>
       <c r="E17" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F17" t="n">
-        <v>14.13855858132909</v>
+        <v>14.04925165968627</v>
       </c>
       <c r="G17" t="n">
-        <v>1.637222600764187</v>
+        <v>1.646949183619512</v>
       </c>
       <c r="H17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I17" t="n">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="J17" t="n">
-        <v>0.005860712924795675</v>
+        <v>0.01426145682407115</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1758213877438703</v>
+        <v>0.4278437047221345</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
@@ -1128,31 +1140,31 @@
         <v>2012</v>
       </c>
       <c r="C18" t="n">
-        <v>10.15808347867631</v>
+        <v>10.31075286872149</v>
       </c>
       <c r="D18" t="n">
-        <v>5.512182622141782</v>
+        <v>5.611423594676724</v>
       </c>
       <c r="E18" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F18" t="n">
-        <v>12.14384609928565</v>
+        <v>12.14287489629747</v>
       </c>
       <c r="G18" t="n">
-        <v>2.318780336500396</v>
+        <v>2.390140708096605</v>
       </c>
       <c r="H18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I18" t="n">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="J18" t="n">
-        <v>0.02855632772107287</v>
+        <v>0.04843865810220309</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8566898316321863</v>
+        <v>1</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
@@ -1168,28 +1180,28 @@
         <v>2013</v>
       </c>
       <c r="C19" t="n">
-        <v>9.693856321706969</v>
+        <v>10.02870471043893</v>
       </c>
       <c r="D19" t="n">
-        <v>5.889230827237123</v>
+        <v>5.627802762865191</v>
       </c>
       <c r="E19" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F19" t="n">
-        <v>9.469303724605963</v>
+        <v>9.488711239852993</v>
       </c>
       <c r="G19" t="n">
-        <v>2.725415838182936</v>
+        <v>2.808154488483488</v>
       </c>
       <c r="H19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I19" t="n">
-        <v>532</v>
+        <v>491</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3286287619001479</v>
+        <v>0.281430428891439</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1208,31 +1220,31 @@
         <v>2014</v>
       </c>
       <c r="C20" t="n">
-        <v>10.61460482735872</v>
+        <v>10.70536880139884</v>
       </c>
       <c r="D20" t="n">
-        <v>3.294963907551784</v>
+        <v>3.463483567948387</v>
       </c>
       <c r="E20" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F20" t="n">
-        <v>13.35679756339063</v>
+        <v>13.47505882419454</v>
       </c>
       <c r="G20" t="n">
-        <v>2.577611329757097</v>
+        <v>2.611815046864939</v>
       </c>
       <c r="H20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I20" t="n">
-        <v>244</v>
+        <v>217</v>
       </c>
       <c r="J20" t="n">
-        <v>0.003849769634387125</v>
+        <v>0.004106174084441311</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1154930890316137</v>
+        <v>0.1231852225332393</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
@@ -1248,28 +1260,28 @@
         <v>2015</v>
       </c>
       <c r="C21" t="n">
-        <v>9.597000873947737</v>
+        <v>9.718650362525967</v>
       </c>
       <c r="D21" t="n">
-        <v>4.200154302701855</v>
+        <v>4.234022268247708</v>
       </c>
       <c r="E21" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F21" t="n">
-        <v>11.08141258044984</v>
+        <v>10.98500206132533</v>
       </c>
       <c r="G21" t="n">
-        <v>2.02707584784693</v>
+        <v>2.051301166179297</v>
       </c>
       <c r="H21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I21" t="n">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1844396099604697</v>
+        <v>0.3012586908215379</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -1288,34 +1300,34 @@
         <v>2016</v>
       </c>
       <c r="C22" t="n">
-        <v>9.447443051048774</v>
+        <v>9.606228664405798</v>
       </c>
       <c r="D22" t="n">
-        <v>3.821423693637831</v>
+        <v>4.041573537770397</v>
       </c>
       <c r="E22" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F22" t="n">
-        <v>12.93129237124124</v>
+        <v>13.33416476440691</v>
       </c>
       <c r="G22" t="n">
-        <v>2.463805392328273</v>
+        <v>1.921074768585109</v>
       </c>
       <c r="H22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I22" t="n">
-        <v>228</v>
+        <v>185</v>
       </c>
       <c r="J22" t="n">
-        <v>0.001897628229057217</v>
+        <v>0.0008605716198518579</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0569288468717165</v>
+        <v>0.02581714859555573</v>
       </c>
       <c r="L22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1328,31 +1340,31 @@
         <v>2017</v>
       </c>
       <c r="C23" t="n">
-        <v>9.500461698874483</v>
+        <v>9.410903727808229</v>
       </c>
       <c r="D23" t="n">
-        <v>4.282009921762072</v>
+        <v>4.340766753501863</v>
       </c>
       <c r="E23" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F23" t="n">
-        <v>11.98921076204066</v>
+        <v>12.09098437557195</v>
       </c>
       <c r="G23" t="n">
-        <v>1.618156329053311</v>
+        <v>1.614310382591607</v>
       </c>
       <c r="H23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I23" t="n">
-        <v>263</v>
+        <v>225</v>
       </c>
       <c r="J23" t="n">
-        <v>0.008433421187829379</v>
+        <v>0.005883133219668732</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2530026356348813</v>
+        <v>0.176493996590062</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
@@ -1368,28 +1380,28 @@
         <v>2018</v>
       </c>
       <c r="C24" t="n">
-        <v>12.83819468595042</v>
+        <v>13.15097977239576</v>
       </c>
       <c r="D24" t="n">
-        <v>3.677566260407265</v>
+        <v>3.448289724495696</v>
       </c>
       <c r="E24" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F24" t="n">
-        <v>12.24311893937339</v>
+        <v>12.23124476044232</v>
       </c>
       <c r="G24" t="n">
-        <v>5.050262909271781</v>
+        <v>5.205461625488588</v>
       </c>
       <c r="H24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I24" t="n">
-        <v>553</v>
+        <v>517</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2077278697847863</v>
+        <v>0.1462192376549335</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
@@ -1408,34 +1420,34 @@
         <v>2019</v>
       </c>
       <c r="C25" t="n">
-        <v>9.442835811448244</v>
+        <v>9.394743583764143</v>
       </c>
       <c r="D25" t="n">
-        <v>3.795607471368923</v>
+        <v>3.784846457500471</v>
       </c>
       <c r="E25" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F25" t="n">
-        <v>12.34243037004431</v>
+        <v>12.66023962966286</v>
       </c>
       <c r="G25" t="n">
-        <v>2.803929060734131</v>
+        <v>2.576111018617653</v>
       </c>
       <c r="H25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I25" t="n">
-        <v>248</v>
+        <v>197</v>
       </c>
       <c r="J25" t="n">
-        <v>0.004563678181715236</v>
+        <v>0.001582868761891829</v>
       </c>
       <c r="K25" t="n">
-        <v>0.1369103454514571</v>
+        <v>0.04748606285675488</v>
       </c>
       <c r="L25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1448,31 +1460,31 @@
         <v>2020</v>
       </c>
       <c r="C26" t="n">
-        <v>9.572395863018597</v>
+        <v>9.947862179664535</v>
       </c>
       <c r="D26" t="n">
-        <v>3.949324898793555</v>
+        <v>3.64205863990138</v>
       </c>
       <c r="E26" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F26" t="n">
-        <v>12.80042532501087</v>
+        <v>12.93112447429792</v>
       </c>
       <c r="G26" t="n">
-        <v>2.943154348106848</v>
+        <v>2.985488873193953</v>
       </c>
       <c r="H26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I26" t="n">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="J26" t="n">
-        <v>0.005175592600620342</v>
+        <v>0.007642297798458144</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1552677780186103</v>
+        <v>0.2292689339537443</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
@@ -1488,31 +1500,31 @@
         <v>2021</v>
       </c>
       <c r="C27" t="n">
-        <v>7.951111992662486</v>
+        <v>7.746552673696294</v>
       </c>
       <c r="D27" t="n">
-        <v>4.442494691607521</v>
+        <v>4.402314055344006</v>
       </c>
       <c r="E27" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F27" t="n">
-        <v>13.3723738071325</v>
+        <v>13.42914484064331</v>
       </c>
       <c r="G27" t="n">
-        <v>2.408530387982349</v>
+        <v>2.471597082863425</v>
       </c>
       <c r="H27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I27" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="J27" t="n">
-        <v>9.587421539495581e-06</v>
+        <v>1.001356489127866e-05</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0002876226461848674</v>
+        <v>0.0003004069467383598</v>
       </c>
       <c r="L27" t="b">
         <v>1</v>
@@ -1528,28 +1540,28 @@
         <v>2022</v>
       </c>
       <c r="C28" t="n">
-        <v>9.951967765989453</v>
+        <v>10.13278087601228</v>
       </c>
       <c r="D28" t="n">
-        <v>5.112772927891278</v>
+        <v>5.08546031403721</v>
       </c>
       <c r="E28" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F28" t="n">
-        <v>10.07180957001096</v>
+        <v>9.841854204885351</v>
       </c>
       <c r="G28" t="n">
-        <v>1.654067090379303</v>
+        <v>1.417033193521666</v>
       </c>
       <c r="H28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I28" t="n">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9838748119668126</v>
+        <v>0.6803032233889605</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
@@ -1568,31 +1580,31 @@
         <v>2023</v>
       </c>
       <c r="C29" t="n">
-        <v>8.99981388463979</v>
+        <v>9.053699378358548</v>
       </c>
       <c r="D29" t="n">
-        <v>3.823377792675793</v>
+        <v>3.883480250300353</v>
       </c>
       <c r="E29" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F29" t="n">
-        <v>16.16987247741761</v>
+        <v>16.40187720981577</v>
       </c>
       <c r="G29" t="n">
-        <v>2.58163056247034</v>
+        <v>2.483208016681455</v>
       </c>
       <c r="H29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I29" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="J29" t="n">
-        <v>6.306281812786463e-08</v>
+        <v>9.944982664154249e-08</v>
       </c>
       <c r="K29" t="n">
-        <v>1.891884543835939e-06</v>
+        <v>2.983494799246275e-06</v>
       </c>
       <c r="L29" t="b">
         <v>1</v>
@@ -1608,28 +1620,28 @@
         <v>2024</v>
       </c>
       <c r="C30" t="n">
-        <v>12.39675251610745</v>
+        <v>12.3284437676128</v>
       </c>
       <c r="D30" t="n">
-        <v>4.850415025313634</v>
+        <v>4.873057616620261</v>
       </c>
       <c r="E30" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F30" t="n">
-        <v>13.04054103655066</v>
+        <v>13.32440515409017</v>
       </c>
       <c r="G30" t="n">
-        <v>3.100841937141716</v>
+        <v>2.974278363104674</v>
       </c>
       <c r="H30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I30" t="n">
-        <v>443</v>
+        <v>377</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8345652426465787</v>
+        <v>0.5777815356954</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -1648,28 +1660,28 @@
         <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>10.4673792693052</v>
+        <v>10.52366261209699</v>
       </c>
       <c r="D31" t="n">
-        <v>3.460673293303018</v>
+        <v>3.368478898115356</v>
       </c>
       <c r="E31" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F31" t="n">
-        <v>11.71610117558562</v>
+        <v>11.8408872373426</v>
       </c>
       <c r="G31" t="n">
-        <v>4.744439612733519</v>
+        <v>4.863316502218911</v>
       </c>
       <c r="H31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I31" t="n">
-        <v>422</v>
+        <v>383</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6228548325569434</v>
+        <v>0.6384401237208024</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
@@ -1688,31 +1700,31 @@
         <v>1996</v>
       </c>
       <c r="C32" t="n">
-        <v>75.10589925325664</v>
+        <v>75.17260123610247</v>
       </c>
       <c r="D32" t="n">
-        <v>15.5913504949599</v>
+        <v>15.86302955935492</v>
       </c>
       <c r="E32" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F32" t="n">
-        <v>85.54669077683077</v>
+        <v>85.21912063117369</v>
       </c>
       <c r="G32" t="n">
-        <v>6.326011670404811</v>
+        <v>6.379297588836915</v>
       </c>
       <c r="H32" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I32" t="n">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="J32" t="n">
-        <v>0.01739754995177921</v>
+        <v>0.03416842526552345</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5219264985533764</v>
+        <v>1</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
@@ -1728,31 +1740,31 @@
         <v>1997</v>
       </c>
       <c r="C33" t="n">
-        <v>71.33539970712428</v>
+        <v>71.28416601892569</v>
       </c>
       <c r="D33" t="n">
-        <v>9.758740583877277</v>
+        <v>10.05180530213313</v>
       </c>
       <c r="E33" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F33" t="n">
-        <v>76.57144698023696</v>
+        <v>76.35399972809067</v>
       </c>
       <c r="G33" t="n">
-        <v>4.901261108377368</v>
+        <v>4.971915300349741</v>
       </c>
       <c r="H33" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I33" t="n">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02084249327931641</v>
+        <v>0.02849757298165726</v>
       </c>
       <c r="K33" t="n">
-        <v>0.6252747983794922</v>
+        <v>0.8549271894497178</v>
       </c>
       <c r="L33" t="b">
         <v>0</v>
@@ -1768,31 +1780,31 @@
         <v>1998</v>
       </c>
       <c r="C34" t="n">
-        <v>69.25593952850382</v>
+        <v>69.31702793763031</v>
       </c>
       <c r="D34" t="n">
-        <v>9.316193397924264</v>
+        <v>9.043173734801307</v>
       </c>
       <c r="E34" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F34" t="n">
-        <v>84.98568990098042</v>
+        <v>84.89503793007469</v>
       </c>
       <c r="G34" t="n">
-        <v>4.101686147512257</v>
+        <v>4.211367512328123</v>
       </c>
       <c r="H34" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I34" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="J34" t="n">
-        <v>2.374284675759496e-07</v>
+        <v>3.735945840881437e-07</v>
       </c>
       <c r="K34" t="n">
-        <v>7.122854027278488e-06</v>
+        <v>1.120783752264431e-05</v>
       </c>
       <c r="L34" t="b">
         <v>1</v>
@@ -1808,31 +1820,31 @@
         <v>1999</v>
       </c>
       <c r="C35" t="n">
-        <v>71.82805445714996</v>
+        <v>71.37135124201887</v>
       </c>
       <c r="D35" t="n">
-        <v>11.65113591976395</v>
+        <v>11.59491919546588</v>
       </c>
       <c r="E35" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F35" t="n">
-        <v>78.80523099556078</v>
+        <v>78.58432059736928</v>
       </c>
       <c r="G35" t="n">
-        <v>6.128599613758417</v>
+        <v>6.251207298104482</v>
       </c>
       <c r="H35" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I35" t="n">
-        <v>284</v>
+        <v>250</v>
       </c>
       <c r="J35" t="n">
-        <v>0.01871055144411147</v>
+        <v>0.01672135374058241</v>
       </c>
       <c r="K35" t="n">
-        <v>0.5613165433233441</v>
+        <v>0.5016406122174724</v>
       </c>
       <c r="L35" t="b">
         <v>0</v>
@@ -1848,34 +1860,34 @@
         <v>2000</v>
       </c>
       <c r="C36" t="n">
-        <v>68.42385289955978</v>
+        <v>67.92854145897184</v>
       </c>
       <c r="D36" t="n">
-        <v>12.25010937036439</v>
+        <v>12.03074858809897</v>
       </c>
       <c r="E36" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F36" t="n">
-        <v>79.04741688458432</v>
+        <v>78.5697443799541</v>
       </c>
       <c r="G36" t="n">
-        <v>6.792321877466493</v>
+        <v>6.718646173076783</v>
       </c>
       <c r="H36" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I36" t="n">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="J36" t="n">
-        <v>0.001373690314189127</v>
+        <v>0.001835264729742047</v>
       </c>
       <c r="K36" t="n">
-        <v>0.04121070942567381</v>
+        <v>0.0550579418922614</v>
       </c>
       <c r="L36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1888,31 +1900,31 @@
         <v>2001</v>
       </c>
       <c r="C37" t="n">
-        <v>74.51689599540553</v>
+        <v>74.0781377294779</v>
       </c>
       <c r="D37" t="n">
-        <v>10.91048302584847</v>
+        <v>10.92509859787909</v>
       </c>
       <c r="E37" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F37" t="n">
-        <v>85.86903855613755</v>
+        <v>85.95122491718593</v>
       </c>
       <c r="G37" t="n">
-        <v>6.463632981858753</v>
+        <v>6.653937376990613</v>
       </c>
       <c r="H37" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I37" t="n">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="J37" t="n">
-        <v>0.0001846869513934674</v>
+        <v>0.0001755568085955835</v>
       </c>
       <c r="K37" t="n">
-        <v>0.005540608541804023</v>
+        <v>0.005266704257867506</v>
       </c>
       <c r="L37" t="b">
         <v>1</v>
@@ -1928,31 +1940,31 @@
         <v>2002</v>
       </c>
       <c r="C38" t="n">
-        <v>73.30905100925538</v>
+        <v>73.79528516116049</v>
       </c>
       <c r="D38" t="n">
-        <v>11.8351845588984</v>
+        <v>11.73514059083849</v>
       </c>
       <c r="E38" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F38" t="n">
-        <v>82.75867933033382</v>
+        <v>82.88686891565705</v>
       </c>
       <c r="G38" t="n">
-        <v>5.345537822731679</v>
+        <v>5.484646236658754</v>
       </c>
       <c r="H38" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I38" t="n">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="J38" t="n">
-        <v>0.002840091429332926</v>
+        <v>0.005148406909865346</v>
       </c>
       <c r="K38" t="n">
-        <v>0.08520274287998778</v>
+        <v>0.1544522072959604</v>
       </c>
       <c r="L38" t="b">
         <v>0</v>
@@ -1968,28 +1980,28 @@
         <v>2003</v>
       </c>
       <c r="C39" t="n">
-        <v>66.19204436890972</v>
+        <v>66.05310518325695</v>
       </c>
       <c r="D39" t="n">
-        <v>11.16571247537133</v>
+        <v>11.34583292820862</v>
       </c>
       <c r="E39" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F39" t="n">
-        <v>71.18506522954357</v>
+        <v>69.8970075206183</v>
       </c>
       <c r="G39" t="n">
-        <v>11.86784023497388</v>
+        <v>11.0201591906457</v>
       </c>
       <c r="H39" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I39" t="n">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="J39" t="n">
-        <v>0.1400983041776397</v>
+        <v>0.2386703829252536</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
@@ -2008,31 +2020,31 @@
         <v>2004</v>
       </c>
       <c r="C40" t="n">
-        <v>73.42816271653325</v>
+        <v>73.48046847645669</v>
       </c>
       <c r="D40" t="n">
-        <v>10.38114666385647</v>
+        <v>10.24678059230835</v>
       </c>
       <c r="E40" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F40" t="n">
-        <v>80.85020500130976</v>
+        <v>81.53502107237263</v>
       </c>
       <c r="G40" t="n">
-        <v>8.928531781783187</v>
+        <v>8.759483740169591</v>
       </c>
       <c r="H40" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I40" t="n">
-        <v>266</v>
+        <v>221</v>
       </c>
       <c r="J40" t="n">
-        <v>0.009492616765089156</v>
+        <v>0.004922587764478395</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2847785029526747</v>
+        <v>0.1476776329343518</v>
       </c>
       <c r="L40" t="b">
         <v>0</v>
@@ -2048,31 +2060,31 @@
         <v>2005</v>
       </c>
       <c r="C41" t="n">
-        <v>69.29716983988872</v>
+        <v>69.5534671417274</v>
       </c>
       <c r="D41" t="n">
-        <v>11.16376956400564</v>
+        <v>11.36147894549377</v>
       </c>
       <c r="E41" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F41" t="n">
-        <v>80.73709791554153</v>
+        <v>80.26792165802402</v>
       </c>
       <c r="G41" t="n">
-        <v>6.739934333841137</v>
+        <v>6.672610911068695</v>
       </c>
       <c r="H41" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I41" t="n">
         <v>197</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0004258812089434185</v>
+        <v>0.001582868761891829</v>
       </c>
       <c r="K41" t="n">
-        <v>0.01277643626830255</v>
+        <v>0.04748606285675488</v>
       </c>
       <c r="L41" t="b">
         <v>1</v>
@@ -2088,28 +2100,28 @@
         <v>2006</v>
       </c>
       <c r="C42" t="n">
-        <v>69.7539035430889</v>
+        <v>69.40801562729003</v>
       </c>
       <c r="D42" t="n">
-        <v>10.83583658060517</v>
+        <v>10.90172058891676</v>
       </c>
       <c r="E42" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F42" t="n">
-        <v>76.46643307330518</v>
+        <v>75.9299458289069</v>
       </c>
       <c r="G42" t="n">
-        <v>10.16384698375655</v>
+        <v>10.24047638177582</v>
       </c>
       <c r="H42" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I42" t="n">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="J42" t="n">
-        <v>0.04257379238605764</v>
+        <v>0.06319220500791187</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
@@ -2128,31 +2140,31 @@
         <v>2007</v>
       </c>
       <c r="C43" t="n">
-        <v>61.57400360433584</v>
+        <v>61.64949293606552</v>
       </c>
       <c r="D43" t="n">
-        <v>10.24502754592404</v>
+        <v>10.54001584306487</v>
       </c>
       <c r="E43" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F43" t="n">
-        <v>80.70249364390951</v>
+        <v>80.3595249585649</v>
       </c>
       <c r="G43" t="n">
-        <v>8.567986396442096</v>
+        <v>8.71773321999812</v>
       </c>
       <c r="H43" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I43" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J43" t="n">
-        <v>3.647105284702372e-07</v>
+        <v>1.644818687053775e-06</v>
       </c>
       <c r="K43" t="n">
-        <v>1.094131585410712e-05</v>
+        <v>4.934456061161324e-05</v>
       </c>
       <c r="L43" t="b">
         <v>1</v>
@@ -2168,31 +2180,31 @@
         <v>2008</v>
       </c>
       <c r="C44" t="n">
-        <v>73.25623075978761</v>
+        <v>73.84769442991268</v>
       </c>
       <c r="D44" t="n">
-        <v>10.86059609586015</v>
+        <v>10.59774894560491</v>
       </c>
       <c r="E44" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F44" t="n">
-        <v>82.1216326804543</v>
+        <v>82.85221367495416</v>
       </c>
       <c r="G44" t="n">
-        <v>6.231555699798406</v>
+        <v>5.673233497773179</v>
       </c>
       <c r="H44" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I44" t="n">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="J44" t="n">
-        <v>0.002378124426629199</v>
+        <v>0.002124174936627585</v>
       </c>
       <c r="K44" t="n">
-        <v>0.07134373279887596</v>
+        <v>0.06372524809882754</v>
       </c>
       <c r="L44" t="b">
         <v>0</v>
@@ -2208,31 +2220,31 @@
         <v>2009</v>
       </c>
       <c r="C45" t="n">
-        <v>68.77134330611291</v>
+        <v>68.62657908427423</v>
       </c>
       <c r="D45" t="n">
-        <v>9.700978915785996</v>
+        <v>9.879942916871746</v>
       </c>
       <c r="E45" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F45" t="n">
-        <v>80.01705217018764</v>
+        <v>80.05338372921449</v>
       </c>
       <c r="G45" t="n">
-        <v>5.013774016412262</v>
+        <v>5.165908517245195</v>
       </c>
       <c r="H45" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I45" t="n">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="J45" t="n">
-        <v>2.545942283368988e-05</v>
+        <v>5.660897667259137e-05</v>
       </c>
       <c r="K45" t="n">
-        <v>0.0007637826850106963</v>
+        <v>0.001698269300177741</v>
       </c>
       <c r="L45" t="b">
         <v>1</v>
@@ -2248,31 +2260,31 @@
         <v>2010</v>
       </c>
       <c r="C46" t="n">
-        <v>74.92066908430775</v>
+        <v>74.50812486949546</v>
       </c>
       <c r="D46" t="n">
-        <v>12.39658330000178</v>
+        <v>12.43144013992758</v>
       </c>
       <c r="E46" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F46" t="n">
-        <v>83.38635197673126</v>
+        <v>83.3034935694471</v>
       </c>
       <c r="G46" t="n">
-        <v>7.625601866314574</v>
+        <v>7.852862713452415</v>
       </c>
       <c r="H46" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I46" t="n">
-        <v>261</v>
+        <v>225</v>
       </c>
       <c r="J46" t="n">
-        <v>0.007787315175456321</v>
+        <v>0.005883133219668732</v>
       </c>
       <c r="K46" t="n">
-        <v>0.2336194552636896</v>
+        <v>0.176493996590062</v>
       </c>
       <c r="L46" t="b">
         <v>0</v>
@@ -2288,31 +2300,31 @@
         <v>2011</v>
       </c>
       <c r="C47" t="n">
-        <v>67.45129722107566</v>
+        <v>67.5146466902799</v>
       </c>
       <c r="D47" t="n">
-        <v>10.45351754777408</v>
+        <v>10.52339826843526</v>
       </c>
       <c r="E47" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F47" t="n">
-        <v>78.78780112810367</v>
+        <v>78.90756969403165</v>
       </c>
       <c r="G47" t="n">
-        <v>5.724080071753527</v>
+        <v>5.879545416105796</v>
       </c>
       <c r="H47" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I47" t="n">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="J47" t="n">
-        <v>9.068357210151884e-05</v>
+        <v>0.0001475293952338924</v>
       </c>
       <c r="K47" t="n">
-        <v>0.002720507163045565</v>
+        <v>0.004425881857016773</v>
       </c>
       <c r="L47" t="b">
         <v>1</v>
@@ -2328,31 +2340,31 @@
         <v>2012</v>
       </c>
       <c r="C48" t="n">
-        <v>68.9330904791377</v>
+        <v>68.62852791485896</v>
       </c>
       <c r="D48" t="n">
-        <v>10.88959550421207</v>
+        <v>10.75544422869377</v>
       </c>
       <c r="E48" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F48" t="n">
-        <v>74.80402856819867</v>
+        <v>74.57660156399966</v>
       </c>
       <c r="G48" t="n">
-        <v>3.267361503062137</v>
+        <v>3.234746925666881</v>
       </c>
       <c r="H48" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I48" t="n">
-        <v>276</v>
+        <v>243</v>
       </c>
       <c r="J48" t="n">
-        <v>0.01393084148473056</v>
+        <v>0.0126318542882927</v>
       </c>
       <c r="K48" t="n">
-        <v>0.4179252445419167</v>
+        <v>0.378955628648781</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
@@ -2368,31 +2380,31 @@
         <v>2013</v>
       </c>
       <c r="C49" t="n">
-        <v>75.19931134489974</v>
+        <v>75.1738044625188</v>
       </c>
       <c r="D49" t="n">
-        <v>9.937725775109952</v>
+        <v>10.05860515373256</v>
       </c>
       <c r="E49" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F49" t="n">
-        <v>80.62855600008639</v>
+        <v>81.68546227500477</v>
       </c>
       <c r="G49" t="n">
-        <v>8.309533085372506</v>
+        <v>7.373872557591785</v>
       </c>
       <c r="H49" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I49" t="n">
-        <v>309</v>
+        <v>256</v>
       </c>
       <c r="J49" t="n">
-        <v>0.04396827738809793</v>
+        <v>0.02110891188788315</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0.6332673566364945</v>
       </c>
       <c r="L49" t="b">
         <v>0</v>
@@ -2408,31 +2420,31 @@
         <v>2014</v>
       </c>
       <c r="C50" t="n">
-        <v>75.62538527270871</v>
+        <v>75.68288361612673</v>
       </c>
       <c r="D50" t="n">
-        <v>7.845935547967382</v>
+        <v>7.835149157309095</v>
       </c>
       <c r="E50" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F50" t="n">
-        <v>84.85518962475564</v>
+        <v>84.94070555979445</v>
       </c>
       <c r="G50" t="n">
-        <v>4.825276421728051</v>
+        <v>4.961267756606207</v>
       </c>
       <c r="H50" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I50" t="n">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="J50" t="n">
-        <v>1.477906509474791e-05</v>
+        <v>3.031375175896113e-05</v>
       </c>
       <c r="K50" t="n">
-        <v>0.0004433719528424374</v>
+        <v>0.0009094125527688338</v>
       </c>
       <c r="L50" t="b">
         <v>1</v>
@@ -2448,31 +2460,31 @@
         <v>2015</v>
       </c>
       <c r="C51" t="n">
-        <v>68.97995184998948</v>
+        <v>68.41782795509383</v>
       </c>
       <c r="D51" t="n">
-        <v>8.66827512522609</v>
+        <v>8.529939372247913</v>
       </c>
       <c r="E51" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F51" t="n">
-        <v>79.46172570471947</v>
+        <v>79.31729542394967</v>
       </c>
       <c r="G51" t="n">
-        <v>4.59674732750715</v>
+        <v>4.700648313312534</v>
       </c>
       <c r="H51" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I51" t="n">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="J51" t="n">
-        <v>2.127131449854637e-05</v>
+        <v>1.812984429586339e-05</v>
       </c>
       <c r="K51" t="n">
-        <v>0.000638139434956391</v>
+        <v>0.0005438953288759018</v>
       </c>
       <c r="L51" t="b">
         <v>1</v>
@@ -2488,31 +2500,31 @@
         <v>2016</v>
       </c>
       <c r="C52" t="n">
-        <v>71.0889067156684</v>
+        <v>70.72579263923579</v>
       </c>
       <c r="D52" t="n">
-        <v>9.259892987145761</v>
+        <v>9.601257110629827</v>
       </c>
       <c r="E52" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F52" t="n">
-        <v>80.66823668752625</v>
+        <v>80.10133529954516</v>
       </c>
       <c r="G52" t="n">
-        <v>7.09752356326271</v>
+        <v>6.932521630254628</v>
       </c>
       <c r="H52" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I52" t="n">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="J52" t="n">
-        <v>0.0004713068645838177</v>
+        <v>0.0009063789671455586</v>
       </c>
       <c r="K52" t="n">
-        <v>0.01413920593751453</v>
+        <v>0.02719136901436676</v>
       </c>
       <c r="L52" t="b">
         <v>1</v>
@@ -2528,31 +2540,31 @@
         <v>2017</v>
       </c>
       <c r="C53" t="n">
-        <v>74.16006209047626</v>
+        <v>74.159309948461</v>
       </c>
       <c r="D53" t="n">
-        <v>9.603403207713582</v>
+        <v>9.836843951260102</v>
       </c>
       <c r="E53" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F53" t="n">
-        <v>84.04512448708992</v>
+        <v>84.15811466491888</v>
       </c>
       <c r="G53" t="n">
-        <v>5.472137377918814</v>
+        <v>5.621278340878813</v>
       </c>
       <c r="H53" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I53" t="n">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0001488455370561887</v>
+        <v>0.0002616151702446423</v>
       </c>
       <c r="K53" t="n">
-        <v>0.004465366111685662</v>
+        <v>0.007848455107339268</v>
       </c>
       <c r="L53" t="b">
         <v>1</v>
@@ -2568,28 +2580,28 @@
         <v>2018</v>
       </c>
       <c r="C54" t="n">
-        <v>68.02540674632576</v>
+        <v>67.9428724694785</v>
       </c>
       <c r="D54" t="n">
-        <v>9.77778337989473</v>
+        <v>9.962511035472227</v>
       </c>
       <c r="E54" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F54" t="n">
-        <v>67.48956879114752</v>
+        <v>67.57446390815241</v>
       </c>
       <c r="G54" t="n">
-        <v>9.099063948604755</v>
+        <v>9.372566508803605</v>
       </c>
       <c r="H54" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I54" t="n">
-        <v>480</v>
+        <v>432</v>
       </c>
       <c r="J54" t="n">
-        <v>0.782378230080268</v>
+        <v>0.8226817986602872</v>
       </c>
       <c r="K54" t="n">
         <v>1</v>
@@ -2608,31 +2620,31 @@
         <v>2019</v>
       </c>
       <c r="C55" t="n">
-        <v>68.16836501251053</v>
+        <v>68.14154047787738</v>
       </c>
       <c r="D55" t="n">
-        <v>11.35321456621267</v>
+        <v>11.75305263802813</v>
       </c>
       <c r="E55" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F55" t="n">
-        <v>77.22884234895724</v>
+        <v>76.21369562981695</v>
       </c>
       <c r="G55" t="n">
-        <v>9.210067645685582</v>
+        <v>8.521035237692896</v>
       </c>
       <c r="H55" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I55" t="n">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="J55" t="n">
-        <v>0.003532293122984995</v>
+        <v>0.009063592599261351</v>
       </c>
       <c r="K55" t="n">
-        <v>0.1059687936895499</v>
+        <v>0.2719077779778405</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
@@ -2648,31 +2660,31 @@
         <v>2020</v>
       </c>
       <c r="C56" t="n">
-        <v>61.55112022126272</v>
+        <v>61.20880198143137</v>
       </c>
       <c r="D56" t="n">
-        <v>10.33609719385209</v>
+        <v>10.09959844130153</v>
       </c>
       <c r="E56" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F56" t="n">
-        <v>75.79037038702199</v>
+        <v>75.43683661260215</v>
       </c>
       <c r="G56" t="n">
-        <v>9.890686783382943</v>
+        <v>10.09034321310621</v>
       </c>
       <c r="H56" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I56" t="n">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="J56" t="n">
-        <v>3.04245205009543e-05</v>
+        <v>5.322930002829426e-05</v>
       </c>
       <c r="K56" t="n">
-        <v>0.000912735615028629</v>
+        <v>0.001596879000848828</v>
       </c>
       <c r="L56" t="b">
         <v>1</v>
@@ -2688,31 +2700,31 @@
         <v>2021</v>
       </c>
       <c r="C57" t="n">
-        <v>71.44671403764232</v>
+        <v>72.17397520506576</v>
       </c>
       <c r="D57" t="n">
-        <v>11.89654024131644</v>
+        <v>11.53258249554697</v>
       </c>
       <c r="E57" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F57" t="n">
-        <v>79.18277415247445</v>
+        <v>78.44752746477354</v>
       </c>
       <c r="G57" t="n">
-        <v>7.968163030404658</v>
+        <v>7.633469571490696</v>
       </c>
       <c r="H57" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I57" t="n">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J57" t="n">
-        <v>0.01501183771754647</v>
+        <v>0.04370873442411537</v>
       </c>
       <c r="K57" t="n">
-        <v>0.4503551315263939</v>
+        <v>1</v>
       </c>
       <c r="L57" t="b">
         <v>0</v>
@@ -2728,31 +2740,31 @@
         <v>2022</v>
       </c>
       <c r="C58" t="n">
-        <v>68.77478877071361</v>
+        <v>68.25741191163111</v>
       </c>
       <c r="D58" t="n">
-        <v>10.15513567623212</v>
+        <v>9.938491263374397</v>
       </c>
       <c r="E58" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F58" t="n">
-        <v>81.97740563810711</v>
+        <v>82.55510587124255</v>
       </c>
       <c r="G58" t="n">
-        <v>4.904771460025843</v>
+        <v>4.45946112305919</v>
       </c>
       <c r="H58" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I58" t="n">
-        <v>140</v>
+        <v>107</v>
       </c>
       <c r="J58" t="n">
-        <v>1.774437115283142e-05</v>
+        <v>8.186260803868183e-06</v>
       </c>
       <c r="K58" t="n">
-        <v>0.0005323311345849427</v>
+        <v>0.0002455878241160455</v>
       </c>
       <c r="L58" t="b">
         <v>1</v>
@@ -2768,28 +2780,28 @@
         <v>2023</v>
       </c>
       <c r="C59" t="n">
-        <v>73.17313688881762</v>
+        <v>72.946677929991</v>
       </c>
       <c r="D59" t="n">
-        <v>10.20377151233914</v>
+        <v>10.46698532192893</v>
       </c>
       <c r="E59" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F59" t="n">
-        <v>71.7850470594492</v>
+        <v>71.6330863526037</v>
       </c>
       <c r="G59" t="n">
-        <v>5.613690801956607</v>
+        <v>5.752439025056738</v>
       </c>
       <c r="H59" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I59" t="n">
-        <v>470</v>
+        <v>421</v>
       </c>
       <c r="J59" t="n">
-        <v>0.8874914582071527</v>
+        <v>0.9481258860583575</v>
       </c>
       <c r="K59" t="n">
         <v>1</v>
@@ -2808,34 +2820,34 @@
         <v>2024</v>
       </c>
       <c r="C60" t="n">
-        <v>67.45145746590323</v>
+        <v>68.04050803722136</v>
       </c>
       <c r="D60" t="n">
-        <v>10.08533178106769</v>
+        <v>10.37878897332623</v>
       </c>
       <c r="E60" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F60" t="n">
-        <v>78.38090488924674</v>
+        <v>77.53615417262003</v>
       </c>
       <c r="G60" t="n">
-        <v>8.307726027651087</v>
+        <v>7.823087120172936</v>
       </c>
       <c r="H60" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I60" t="n">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="J60" t="n">
-        <v>0.0005479855612614606</v>
+        <v>0.00296741941559111</v>
       </c>
       <c r="K60" t="n">
-        <v>0.01643956683784382</v>
+        <v>0.0890225824677333</v>
       </c>
       <c r="L60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -2848,31 +2860,31 @@
         <v>2025</v>
       </c>
       <c r="C61" t="n">
-        <v>69.37173398269509</v>
+        <v>69.049592685845</v>
       </c>
       <c r="D61" t="n">
-        <v>10.21870594770376</v>
+        <v>10.19654801250745</v>
       </c>
       <c r="E61" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F61" t="n">
-        <v>78.33383580014049</v>
+        <v>78.37446632061568</v>
       </c>
       <c r="G61" t="n">
-        <v>7.413848899747866</v>
+        <v>7.640184124827196</v>
       </c>
       <c r="H61" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I61" t="n">
-        <v>215</v>
+        <v>184</v>
       </c>
       <c r="J61" t="n">
-        <v>0.001034514663497209</v>
+        <v>0.0008169189737809551</v>
       </c>
       <c r="K61" t="n">
-        <v>0.03103543990491627</v>
+        <v>0.02450756921342865</v>
       </c>
       <c r="L61" t="b">
         <v>1</v>
@@ -2888,28 +2900,28 @@
         <v>1996</v>
       </c>
       <c r="C62" t="n">
-        <v>98.89828034091231</v>
+        <v>98.43242384985489</v>
       </c>
       <c r="D62" t="n">
-        <v>21.10021547064305</v>
+        <v>21.37779945291916</v>
       </c>
       <c r="E62" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F62" t="n">
-        <v>101.8766224338586</v>
+        <v>101.5392478063965</v>
       </c>
       <c r="G62" t="n">
-        <v>7.315092630318611</v>
+        <v>7.410804516696374</v>
       </c>
       <c r="H62" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I62" t="n">
-        <v>513</v>
+        <v>457</v>
       </c>
       <c r="J62" t="n">
-        <v>0.4709896409740194</v>
+        <v>0.5581820784164472</v>
       </c>
       <c r="K62" t="n">
         <v>1</v>
@@ -2928,31 +2940,31 @@
         <v>1997</v>
       </c>
       <c r="C63" t="n">
-        <v>105.1838214296944</v>
+        <v>104.7763834396566</v>
       </c>
       <c r="D63" t="n">
-        <v>14.03770508313767</v>
+        <v>13.79918278775266</v>
       </c>
       <c r="E63" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F63" t="n">
-        <v>36.02301127187355</v>
+        <v>35.33683130484003</v>
       </c>
       <c r="G63" t="n">
-        <v>8.16475377521348</v>
+        <v>7.926242765099441</v>
       </c>
       <c r="H63" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I63" t="n">
-        <v>918</v>
+        <v>832</v>
       </c>
       <c r="J63" t="n">
-        <v>6.495105957484229e-10</v>
+        <v>1.88700683005307e-09</v>
       </c>
       <c r="K63" t="n">
-        <v>1.948531787245269e-08</v>
+        <v>5.661020490159211e-08</v>
       </c>
       <c r="L63" t="b">
         <v>1</v>
@@ -2968,31 +2980,31 @@
         <v>1998</v>
       </c>
       <c r="C64" t="n">
-        <v>84.03207011143596</v>
+        <v>83.75970193124155</v>
       </c>
       <c r="D64" t="n">
-        <v>23.13680066968022</v>
+        <v>23.48457810728369</v>
       </c>
       <c r="E64" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F64" t="n">
-        <v>105.6182477814219</v>
+        <v>105.2490206623264</v>
       </c>
       <c r="G64" t="n">
-        <v>12.08418463589851</v>
+        <v>12.36271211733314</v>
       </c>
       <c r="H64" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I64" t="n">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="J64" t="n">
-        <v>0.0004258812089434185</v>
+        <v>0.0009063789671455586</v>
       </c>
       <c r="K64" t="n">
-        <v>0.01277643626830255</v>
+        <v>0.02719136901436676</v>
       </c>
       <c r="L64" t="b">
         <v>1</v>
@@ -3008,31 +3020,31 @@
         <v>1999</v>
       </c>
       <c r="C65" t="n">
-        <v>101.9558055791424</v>
+        <v>101.756853404167</v>
       </c>
       <c r="D65" t="n">
-        <v>14.09173831754737</v>
+        <v>14.2391646512915</v>
       </c>
       <c r="E65" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F65" t="n">
-        <v>53.03066882003292</v>
+        <v>52.20815666572314</v>
       </c>
       <c r="G65" t="n">
-        <v>11.88089304515075</v>
+        <v>11.76762081409923</v>
       </c>
       <c r="H65" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I65" t="n">
-        <v>912</v>
+        <v>827</v>
       </c>
       <c r="J65" t="n">
-        <v>1.080260810730017e-09</v>
+        <v>2.939225416547013e-09</v>
       </c>
       <c r="K65" t="n">
-        <v>3.240782432190051e-08</v>
+        <v>8.817676249641038e-08</v>
       </c>
       <c r="L65" t="b">
         <v>1</v>
@@ -3048,28 +3060,28 @@
         <v>2000</v>
       </c>
       <c r="C66" t="n">
-        <v>81.71504817016255</v>
+        <v>80.56215963770144</v>
       </c>
       <c r="D66" t="n">
-        <v>26.62395312062671</v>
+        <v>25.92371097823655</v>
       </c>
       <c r="E66" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F66" t="n">
-        <v>78.09967899302372</v>
+        <v>77.71183802717232</v>
       </c>
       <c r="G66" t="n">
-        <v>10.35846637133823</v>
+        <v>10.55683613648312</v>
       </c>
       <c r="H66" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I66" t="n">
-        <v>487</v>
+        <v>437</v>
       </c>
       <c r="J66" t="n">
-        <v>0.7109797774578576</v>
+        <v>0.7669350082286583</v>
       </c>
       <c r="K66" t="n">
         <v>1</v>
@@ -3088,28 +3100,28 @@
         <v>2001</v>
       </c>
       <c r="C67" t="n">
-        <v>106.1361970206829</v>
+        <v>105.6677888697769</v>
       </c>
       <c r="D67" t="n">
-        <v>15.09107759900871</v>
+        <v>15.38917092272576</v>
       </c>
       <c r="E67" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F67" t="n">
-        <v>115.3314263831765</v>
+        <v>115.1643309510326</v>
       </c>
       <c r="G67" t="n">
-        <v>5.273108144127851</v>
+        <v>5.391555325215465</v>
       </c>
       <c r="H67" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I67" t="n">
-        <v>317</v>
+        <v>286</v>
       </c>
       <c r="J67" t="n">
-        <v>0.05657247031415955</v>
+        <v>0.06116585851415507</v>
       </c>
       <c r="K67" t="n">
         <v>1</v>
@@ -3128,28 +3140,28 @@
         <v>2002</v>
       </c>
       <c r="C68" t="n">
-        <v>97.3013016951283</v>
+        <v>97.0688009754184</v>
       </c>
       <c r="D68" t="n">
-        <v>15.86697941785119</v>
+        <v>16.32612102082575</v>
       </c>
       <c r="E68" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F68" t="n">
-        <v>92.93442100531107</v>
+        <v>91.97753396546827</v>
       </c>
       <c r="G68" t="n">
-        <v>13.11511243456149</v>
+        <v>12.93022823996404</v>
       </c>
       <c r="H68" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I68" t="n">
-        <v>546</v>
+        <v>507</v>
       </c>
       <c r="J68" t="n">
-        <v>0.2438092084109198</v>
+        <v>0.1907249489634856</v>
       </c>
       <c r="K68" t="n">
         <v>1</v>
@@ -3168,31 +3180,31 @@
         <v>2003</v>
       </c>
       <c r="C69" t="n">
-        <v>81.4812904781373</v>
+        <v>81.26216279474836</v>
       </c>
       <c r="D69" t="n">
-        <v>14.44003058011268</v>
+        <v>14.64125572897841</v>
       </c>
       <c r="E69" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F69" t="n">
-        <v>45.04368292236222</v>
+        <v>43.44360670817997</v>
       </c>
       <c r="G69" t="n">
-        <v>8.777466955172089</v>
+        <v>6.191528517514764</v>
       </c>
       <c r="H69" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I69" t="n">
-        <v>893</v>
+        <v>818</v>
       </c>
       <c r="J69" t="n">
-        <v>5.186775483567806e-09</v>
+        <v>6.442898560667814e-09</v>
       </c>
       <c r="K69" t="n">
-        <v>1.556032645070342e-07</v>
+        <v>1.932869568200344e-07</v>
       </c>
       <c r="L69" t="b">
         <v>1</v>
@@ -3208,34 +3220,34 @@
         <v>2004</v>
       </c>
       <c r="C70" t="n">
-        <v>99.18895797297412</v>
+        <v>99.20804557033657</v>
       </c>
       <c r="D70" t="n">
-        <v>16.26757993409594</v>
+        <v>16.58378601636846</v>
       </c>
       <c r="E70" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F70" t="n">
-        <v>72.64477914120637</v>
+        <v>72.46957401641656</v>
       </c>
       <c r="G70" t="n">
-        <v>29.04848853345857</v>
+        <v>29.93378121371545</v>
       </c>
       <c r="H70" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I70" t="n">
-        <v>693</v>
+        <v>614</v>
       </c>
       <c r="J70" t="n">
-        <v>0.001653921362135666</v>
+        <v>0.00429785990742613</v>
       </c>
       <c r="K70" t="n">
-        <v>0.04961764086406999</v>
+        <v>0.1289357972227839</v>
       </c>
       <c r="L70" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -3248,28 +3260,28 @@
         <v>2005</v>
       </c>
       <c r="C71" t="n">
-        <v>88.40892568481289</v>
+        <v>88.20793028369859</v>
       </c>
       <c r="D71" t="n">
-        <v>18.5962736852517</v>
+        <v>18.93247790920579</v>
       </c>
       <c r="E71" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F71" t="n">
-        <v>90.81928938912085</v>
+        <v>90.19305689215946</v>
       </c>
       <c r="G71" t="n">
-        <v>14.74553327313778</v>
+        <v>14.97842889272038</v>
       </c>
       <c r="H71" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I71" t="n">
-        <v>404</v>
+        <v>374</v>
       </c>
       <c r="J71" t="n">
-        <v>0.4627391224136692</v>
+        <v>0.5485050746029028</v>
       </c>
       <c r="K71" t="n">
         <v>1</v>
@@ -3288,31 +3300,31 @@
         <v>2006</v>
       </c>
       <c r="C72" t="n">
-        <v>94.38607709322656</v>
+        <v>93.61412397395954</v>
       </c>
       <c r="D72" t="n">
-        <v>21.37287975303705</v>
+        <v>21.39617055213461</v>
       </c>
       <c r="E72" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F72" t="n">
-        <v>37.60736617771921</v>
+        <v>33.13379068780065</v>
       </c>
       <c r="G72" t="n">
-        <v>27.38346182971953</v>
+        <v>21.36588250817031</v>
       </c>
       <c r="H72" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I72" t="n">
-        <v>839</v>
+        <v>792</v>
       </c>
       <c r="J72" t="n">
-        <v>3.163117192357612e-07</v>
+        <v>5.669246052395953e-08</v>
       </c>
       <c r="K72" t="n">
-        <v>9.489351577072836e-06</v>
+        <v>1.700773815718786e-06</v>
       </c>
       <c r="L72" t="b">
         <v>1</v>
@@ -3328,31 +3340,31 @@
         <v>2007</v>
       </c>
       <c r="C73" t="n">
-        <v>65.86730540617029</v>
+        <v>65.49940538657482</v>
       </c>
       <c r="D73" t="n">
-        <v>29.15626380453561</v>
+        <v>29.88277483994739</v>
       </c>
       <c r="E73" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F73" t="n">
-        <v>104.7312205923974</v>
+        <v>104.3232228276249</v>
       </c>
       <c r="G73" t="n">
-        <v>17.78337039105716</v>
+        <v>18.25332632362155</v>
       </c>
       <c r="H73" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I73" t="n">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="J73" t="n">
-        <v>1.307153442677531e-05</v>
+        <v>3.229643088941764e-05</v>
       </c>
       <c r="K73" t="n">
-        <v>0.0003921460328032593</v>
+        <v>0.0009688929266825293</v>
       </c>
       <c r="L73" t="b">
         <v>1</v>
@@ -3368,34 +3380,34 @@
         <v>2008</v>
       </c>
       <c r="C74" t="n">
-        <v>101.1724618674715</v>
+        <v>100.9556637418622</v>
       </c>
       <c r="D74" t="n">
-        <v>22.85709615179879</v>
+        <v>23.29871785186049</v>
       </c>
       <c r="E74" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F74" t="n">
-        <v>81.5733434341752</v>
+        <v>81.26335798188504</v>
       </c>
       <c r="G74" t="n">
-        <v>15.53245396381499</v>
+        <v>15.95939064785754</v>
       </c>
       <c r="H74" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I74" t="n">
-        <v>699</v>
+        <v>629</v>
       </c>
       <c r="J74" t="n">
-        <v>0.00125064321280691</v>
+        <v>0.002124174936627585</v>
       </c>
       <c r="K74" t="n">
-        <v>0.03751929638420731</v>
+        <v>0.06372524809882754</v>
       </c>
       <c r="L74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -3408,31 +3420,31 @@
         <v>2009</v>
       </c>
       <c r="C75" t="n">
-        <v>79.72293298109879</v>
+        <v>78.86187691872232</v>
       </c>
       <c r="D75" t="n">
-        <v>13.39591569181862</v>
+        <v>12.74370052644178</v>
       </c>
       <c r="E75" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F75" t="n">
-        <v>41.06625164416173</v>
+        <v>39.11338239456549</v>
       </c>
       <c r="G75" t="n">
-        <v>16.3141064905288</v>
+        <v>14.76318322021093</v>
       </c>
       <c r="H75" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I75" t="n">
-        <v>883</v>
+        <v>813</v>
       </c>
       <c r="J75" t="n">
-        <v>1.154419607272862e-08</v>
+        <v>9.893374572312544e-09</v>
       </c>
       <c r="K75" t="n">
-        <v>3.463258821818587e-07</v>
+        <v>2.968012371693763e-07</v>
       </c>
       <c r="L75" t="b">
         <v>1</v>
@@ -3448,28 +3460,28 @@
         <v>2010</v>
       </c>
       <c r="C76" t="n">
-        <v>103.4731755616355</v>
+        <v>102.6105740381891</v>
       </c>
       <c r="D76" t="n">
-        <v>17.27382565377077</v>
+        <v>17.07313627601567</v>
       </c>
       <c r="E76" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F76" t="n">
-        <v>111.6072266529027</v>
+        <v>112.0412563685251</v>
       </c>
       <c r="G76" t="n">
-        <v>18.67071156398673</v>
+        <v>19.16194657911744</v>
       </c>
       <c r="H76" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I76" t="n">
-        <v>359</v>
+        <v>307</v>
       </c>
       <c r="J76" t="n">
-        <v>0.1800233838508485</v>
+        <v>0.1167226952455683</v>
       </c>
       <c r="K76" t="n">
         <v>1</v>
@@ -3488,28 +3500,28 @@
         <v>2011</v>
       </c>
       <c r="C77" t="n">
-        <v>80.3673829816229</v>
+        <v>80.33220372749233</v>
       </c>
       <c r="D77" t="n">
-        <v>14.93367793744468</v>
+        <v>15.2065814815394</v>
       </c>
       <c r="E77" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F77" t="n">
-        <v>89.8220888763089</v>
+        <v>91.62256828474365</v>
       </c>
       <c r="G77" t="n">
-        <v>20.88196491499657</v>
+        <v>20.2039759373554</v>
       </c>
       <c r="H77" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I77" t="n">
-        <v>346</v>
+        <v>285</v>
       </c>
       <c r="J77" t="n">
-        <v>0.1295578784361326</v>
+        <v>0.05919362731886423</v>
       </c>
       <c r="K77" t="n">
         <v>1</v>
@@ -3528,31 +3540,31 @@
         <v>2012</v>
       </c>
       <c r="C78" t="n">
-        <v>88.33158924846148</v>
+        <v>88.47241720917056</v>
       </c>
       <c r="D78" t="n">
-        <v>13.34981978155296</v>
+        <v>13.53276938380504</v>
       </c>
       <c r="E78" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F78" t="n">
-        <v>73.12294334093664</v>
+        <v>73.01528941409561</v>
       </c>
       <c r="G78" t="n">
-        <v>9.327335470299731</v>
+        <v>9.604145818660186</v>
       </c>
       <c r="H78" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I78" t="n">
-        <v>746</v>
+        <v>676</v>
       </c>
       <c r="J78" t="n">
-        <v>0.0001132206983753518</v>
+        <v>0.0001755568085955835</v>
       </c>
       <c r="K78" t="n">
-        <v>0.003396620951260554</v>
+        <v>0.005266704257867506</v>
       </c>
       <c r="L78" t="b">
         <v>1</v>
@@ -3568,31 +3580,31 @@
         <v>2013</v>
       </c>
       <c r="C79" t="n">
-        <v>99.5986975710494</v>
+        <v>99.37842104117198</v>
       </c>
       <c r="D79" t="n">
-        <v>12.51776380417007</v>
+        <v>12.60260384301435</v>
       </c>
       <c r="E79" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F79" t="n">
-        <v>66.5566454104993</v>
+        <v>67.56291819983014</v>
       </c>
       <c r="G79" t="n">
-        <v>7.067461262268964</v>
+        <v>5.988061287738817</v>
       </c>
       <c r="H79" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I79" t="n">
-        <v>902</v>
+        <v>816</v>
       </c>
       <c r="J79" t="n">
-        <v>2.486600410834315e-09</v>
+        <v>7.653355924998167e-09</v>
       </c>
       <c r="K79" t="n">
-        <v>7.459801232502945e-08</v>
+        <v>2.29600677749945e-07</v>
       </c>
       <c r="L79" t="b">
         <v>1</v>
@@ -3608,31 +3620,31 @@
         <v>2014</v>
       </c>
       <c r="C80" t="n">
-        <v>93.80121457999164</v>
+        <v>93.72661814975268</v>
       </c>
       <c r="D80" t="n">
-        <v>13.16066023757403</v>
+        <v>13.45192243905415</v>
       </c>
       <c r="E80" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F80" t="n">
-        <v>102.708535322422</v>
+        <v>103.7923414944804</v>
       </c>
       <c r="G80" t="n">
-        <v>11.67146320433267</v>
+        <v>11.16996800564622</v>
       </c>
       <c r="H80" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I80" t="n">
-        <v>283</v>
+        <v>237</v>
       </c>
       <c r="J80" t="n">
-        <v>0.01804359278294268</v>
+        <v>0.009859154750988497</v>
       </c>
       <c r="K80" t="n">
-        <v>0.5413077834882803</v>
+        <v>0.2957746425296549</v>
       </c>
       <c r="L80" t="b">
         <v>0</v>
@@ -3648,31 +3660,31 @@
         <v>2015</v>
       </c>
       <c r="C81" t="n">
-        <v>91.92281011835477</v>
+        <v>90.83564665026432</v>
       </c>
       <c r="D81" t="n">
-        <v>21.6309622720843</v>
+        <v>21.51058547020879</v>
       </c>
       <c r="E81" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F81" t="n">
-        <v>62.03658746940607</v>
+        <v>63.13228488536651</v>
       </c>
       <c r="G81" t="n">
-        <v>9.696202172253898</v>
+        <v>8.915321617066146</v>
       </c>
       <c r="H81" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I81" t="n">
-        <v>810</v>
+        <v>722</v>
       </c>
       <c r="J81" t="n">
-        <v>2.327253458076122e-06</v>
+        <v>1.001356489127866e-05</v>
       </c>
       <c r="K81" t="n">
-        <v>6.981760374228365e-05</v>
+        <v>0.0003004069467383598</v>
       </c>
       <c r="L81" t="b">
         <v>1</v>
@@ -3688,34 +3700,34 @@
         <v>2016</v>
       </c>
       <c r="C82" t="n">
-        <v>94.47450136805331</v>
+        <v>93.74142840035681</v>
       </c>
       <c r="D82" t="n">
-        <v>20.09970237569153</v>
+        <v>20.48669847214587</v>
       </c>
       <c r="E82" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F82" t="n">
-        <v>77.1854797622416</v>
+        <v>74.14710338239445</v>
       </c>
       <c r="G82" t="n">
-        <v>19.67243135917556</v>
+        <v>15.9453100587569</v>
       </c>
       <c r="H82" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I82" t="n">
-        <v>677</v>
+        <v>638</v>
       </c>
       <c r="J82" t="n">
-        <v>0.003382658376515372</v>
+        <v>0.001362786499301514</v>
       </c>
       <c r="K82" t="n">
-        <v>0.1014797512954612</v>
+        <v>0.04088359497904541</v>
       </c>
       <c r="L82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -3728,31 +3740,31 @@
         <v>2017</v>
       </c>
       <c r="C83" t="n">
-        <v>94.31387803880851</v>
+        <v>94.37132574190579</v>
       </c>
       <c r="D83" t="n">
-        <v>13.04225737754241</v>
+        <v>13.51031395731919</v>
       </c>
       <c r="E83" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F83" t="n">
-        <v>78.74804515409323</v>
+        <v>75.74853099348988</v>
       </c>
       <c r="G83" t="n">
-        <v>18.71283256077347</v>
+        <v>14.80220542541867</v>
       </c>
       <c r="H83" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I83" t="n">
-        <v>713</v>
+        <v>683</v>
       </c>
       <c r="J83" t="n">
-        <v>0.0006361594424557884</v>
+        <v>0.0001166683149075125</v>
       </c>
       <c r="K83" t="n">
-        <v>0.01908478327367365</v>
+        <v>0.003500049447225374</v>
       </c>
       <c r="L83" t="b">
         <v>1</v>
@@ -3768,31 +3780,31 @@
         <v>2018</v>
       </c>
       <c r="C84" t="n">
-        <v>81.50736924867114</v>
+        <v>80.41177404254381</v>
       </c>
       <c r="D84" t="n">
-        <v>18.17000469013475</v>
+        <v>17.93448643894412</v>
       </c>
       <c r="E84" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F84" t="n">
-        <v>58.00912838614067</v>
+        <v>58.27943850834976</v>
       </c>
       <c r="G84" t="n">
-        <v>37.26764143272195</v>
+        <v>38.39843444755837</v>
       </c>
       <c r="H84" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I84" t="n">
-        <v>632</v>
+        <v>553</v>
       </c>
       <c r="J84" t="n">
-        <v>0.0201094347499822</v>
+        <v>0.04843865810220309</v>
       </c>
       <c r="K84" t="n">
-        <v>0.603283042499466</v>
+        <v>1</v>
       </c>
       <c r="L84" t="b">
         <v>0</v>
@@ -3808,31 +3820,31 @@
         <v>2019</v>
       </c>
       <c r="C85" t="n">
-        <v>85.09051902171048</v>
+        <v>84.43285364366722</v>
       </c>
       <c r="D85" t="n">
-        <v>21.97821254771522</v>
+        <v>22.17677451099241</v>
       </c>
       <c r="E85" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F85" t="n">
-        <v>72.18428331196607</v>
+        <v>68.47717131333138</v>
       </c>
       <c r="G85" t="n">
-        <v>20.67294543136362</v>
+        <v>14.84775372106789</v>
       </c>
       <c r="H85" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I85" t="n">
-        <v>627</v>
+        <v>595</v>
       </c>
       <c r="J85" t="n">
-        <v>0.02401252830361675</v>
+        <v>0.009859154750988497</v>
       </c>
       <c r="K85" t="n">
-        <v>0.7203758491085024</v>
+        <v>0.2957746425296549</v>
       </c>
       <c r="L85" t="b">
         <v>0</v>
@@ -3848,28 +3860,28 @@
         <v>2020</v>
       </c>
       <c r="C86" t="n">
-        <v>65.27698545984414</v>
+        <v>64.50214439678626</v>
       </c>
       <c r="D86" t="n">
-        <v>19.06730688038486</v>
+        <v>18.74511057344082</v>
       </c>
       <c r="E86" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F86" t="n">
-        <v>71.44389737100597</v>
+        <v>70.01372983300294</v>
       </c>
       <c r="G86" t="n">
-        <v>40.45550288005872</v>
+        <v>41.28155458777518</v>
       </c>
       <c r="H86" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I86" t="n">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="J86" t="n">
-        <v>0.5945660460528879</v>
+        <v>0.811450732731845</v>
       </c>
       <c r="K86" t="n">
         <v>1</v>
@@ -3888,31 +3900,31 @@
         <v>2021</v>
       </c>
       <c r="C87" t="n">
-        <v>103.4476440125376</v>
+        <v>103.8113599251015</v>
       </c>
       <c r="D87" t="n">
-        <v>14.2943732693235</v>
+        <v>14.37854697775223</v>
       </c>
       <c r="E87" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F87" t="n">
-        <v>83.49482659296379</v>
+        <v>83.18168305972259</v>
       </c>
       <c r="G87" t="n">
-        <v>6.028250803489382</v>
+        <v>6.07816130940498</v>
       </c>
       <c r="H87" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I87" t="n">
-        <v>796</v>
+        <v>725</v>
       </c>
       <c r="J87" t="n">
-        <v>5.785817796279661e-06</v>
+        <v>8.186260803868183e-06</v>
       </c>
       <c r="K87" t="n">
-        <v>0.0001735745338883898</v>
+        <v>0.0002455878241160455</v>
       </c>
       <c r="L87" t="b">
         <v>1</v>
@@ -3928,31 +3940,31 @@
         <v>2022</v>
       </c>
       <c r="C88" t="n">
-        <v>81.44622930884447</v>
+        <v>81.42646051514276</v>
       </c>
       <c r="D88" t="n">
-        <v>22.835842445694</v>
+        <v>23.19257184955166</v>
       </c>
       <c r="E88" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F88" t="n">
-        <v>114.6931562911037</v>
+        <v>115.4513826776107</v>
       </c>
       <c r="G88" t="n">
-        <v>9.249016592987681</v>
+        <v>9.006520075985101</v>
       </c>
       <c r="H88" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I88" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="J88" t="n">
-        <v>2.741427770435808e-07</v>
+        <v>5.057698801703079e-07</v>
       </c>
       <c r="K88" t="n">
-        <v>8.224283311307424e-06</v>
+        <v>1.517309640510924e-05</v>
       </c>
       <c r="L88" t="b">
         <v>1</v>
@@ -3968,31 +3980,31 @@
         <v>2023</v>
       </c>
       <c r="C89" t="n">
-        <v>98.94106792045348</v>
+        <v>98.13605957020596</v>
       </c>
       <c r="D89" t="n">
-        <v>20.81843950346574</v>
+        <v>20.8731370246531</v>
       </c>
       <c r="E89" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F89" t="n">
-        <v>23.59012537253787</v>
+        <v>22.56259623549386</v>
       </c>
       <c r="G89" t="n">
-        <v>9.574072894180027</v>
+        <v>8.913076186281025</v>
       </c>
       <c r="H89" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I89" t="n">
-        <v>918</v>
+        <v>832</v>
       </c>
       <c r="J89" t="n">
-        <v>6.495105957484229e-10</v>
+        <v>1.88700683005307e-09</v>
       </c>
       <c r="K89" t="n">
-        <v>1.948531787245269e-08</v>
+        <v>5.661020490159211e-08</v>
       </c>
       <c r="L89" t="b">
         <v>1</v>
@@ -4008,31 +4020,31 @@
         <v>2024</v>
       </c>
       <c r="C90" t="n">
-        <v>79.10104642995658</v>
+        <v>79.07892573319678</v>
       </c>
       <c r="D90" t="n">
-        <v>16.73473607909403</v>
+        <v>16.97202104859291</v>
       </c>
       <c r="E90" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F90" t="n">
-        <v>106.8420339321685</v>
+        <v>106.0352175912817</v>
       </c>
       <c r="G90" t="n">
-        <v>11.54153012154811</v>
+        <v>11.42217823178189</v>
       </c>
       <c r="H90" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I90" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J90" t="n">
-        <v>6.861502641248148e-07</v>
+        <v>2.191053216980323e-06</v>
       </c>
       <c r="K90" t="n">
-        <v>2.058450792374444e-05</v>
+        <v>6.57315965094097e-05</v>
       </c>
       <c r="L90" t="b">
         <v>1</v>
@@ -4048,28 +4060,28 @@
         <v>2025</v>
       </c>
       <c r="C91" t="n">
-        <v>80.98086119235558</v>
+        <v>80.74232794095224</v>
       </c>
       <c r="D91" t="n">
-        <v>17.21345042056316</v>
+        <v>17.43494833399994</v>
       </c>
       <c r="E91" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F91" t="n">
-        <v>89.34683937996344</v>
+        <v>88.52665157090266</v>
       </c>
       <c r="G91" t="n">
-        <v>24.35287881809692</v>
+        <v>24.87354195090092</v>
       </c>
       <c r="H91" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I91" t="n">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="J91" t="n">
-        <v>0.0882902405265886</v>
+        <v>0.1383583859017258</v>
       </c>
       <c r="K91" t="n">
         <v>1</v>
@@ -4088,28 +4100,28 @@
         <v>1996</v>
       </c>
       <c r="C92" t="n">
-        <v>9.992769562055786</v>
+        <v>10.27363294450421</v>
       </c>
       <c r="D92" t="n">
-        <v>5.021670158881061</v>
+        <v>4.818658128888899</v>
       </c>
       <c r="E92" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F92" t="n">
-        <v>10.59886264300705</v>
+        <v>10.602605692049</v>
       </c>
       <c r="G92" t="n">
-        <v>1.305355798641909</v>
+        <v>1.345441449502483</v>
       </c>
       <c r="H92" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I92" t="n">
-        <v>471</v>
+        <v>442</v>
       </c>
       <c r="J92" t="n">
-        <v>0.8768581211149143</v>
+        <v>0.7123694118406746</v>
       </c>
       <c r="K92" t="n">
         <v>1</v>
@@ -4128,31 +4140,31 @@
         <v>1997</v>
       </c>
       <c r="C93" t="n">
-        <v>10.78928973175364</v>
+        <v>10.97660089530816</v>
       </c>
       <c r="D93" t="n">
-        <v>5.61557783640082</v>
+        <v>5.528867928745404</v>
       </c>
       <c r="E93" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F93" t="n">
-        <v>13.65365007050652</v>
+        <v>13.74790717539859</v>
       </c>
       <c r="G93" t="n">
-        <v>1.459955721451492</v>
+        <v>1.453840705476907</v>
       </c>
       <c r="H93" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I93" t="n">
-        <v>268</v>
+        <v>244</v>
       </c>
       <c r="J93" t="n">
-        <v>0.01026313276460232</v>
+        <v>0.01315574073834637</v>
       </c>
       <c r="K93" t="n">
-        <v>0.3078939829380696</v>
+        <v>0.3946722221503912</v>
       </c>
       <c r="L93" t="b">
         <v>0</v>
@@ -4168,28 +4180,28 @@
         <v>1998</v>
       </c>
       <c r="C94" t="n">
-        <v>13.07873614475737</v>
+        <v>13.14782076313963</v>
       </c>
       <c r="D94" t="n">
-        <v>4.188520106073605</v>
+        <v>4.214970116356376</v>
       </c>
       <c r="E94" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F94" t="n">
-        <v>12.498962819752</v>
+        <v>12.797415663304</v>
       </c>
       <c r="G94" t="n">
-        <v>2.667627847570123</v>
+        <v>2.459012714879631</v>
       </c>
       <c r="H94" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I94" t="n">
-        <v>486</v>
+        <v>423</v>
       </c>
       <c r="J94" t="n">
-        <v>0.7210421448305544</v>
+        <v>0.9251280814116045</v>
       </c>
       <c r="K94" t="n">
         <v>1</v>
@@ -4208,31 +4220,31 @@
         <v>1999</v>
       </c>
       <c r="C95" t="n">
-        <v>11.95587032416945</v>
+        <v>12.07225650204006</v>
       </c>
       <c r="D95" t="n">
-        <v>3.282957650166607</v>
+        <v>3.196867673996539</v>
       </c>
       <c r="E95" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F95" t="n">
-        <v>15.82146334615846</v>
+        <v>16.15111827475861</v>
       </c>
       <c r="G95" t="n">
-        <v>2.468258194402768</v>
+        <v>2.150729375867636</v>
       </c>
       <c r="H95" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I95" t="n">
-        <v>163</v>
+        <v>120</v>
       </c>
       <c r="J95" t="n">
-        <v>6.844527373022116e-05</v>
+        <v>1.934656977527742e-05</v>
       </c>
       <c r="K95" t="n">
-        <v>0.002053358211906635</v>
+        <v>0.0005803970932583226</v>
       </c>
       <c r="L95" t="b">
         <v>1</v>
@@ -4248,28 +4260,28 @@
         <v>2000</v>
       </c>
       <c r="C96" t="n">
-        <v>14.47625957663919</v>
+        <v>14.78314277787508</v>
       </c>
       <c r="D96" t="n">
-        <v>5.528534246460251</v>
+        <v>5.355376696778997</v>
       </c>
       <c r="E96" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F96" t="n">
-        <v>14.04626729963051</v>
+        <v>13.95035253281263</v>
       </c>
       <c r="G96" t="n">
-        <v>1.815867108567398</v>
+        <v>1.829498638516049</v>
       </c>
       <c r="H96" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I96" t="n">
-        <v>526</v>
+        <v>497</v>
       </c>
       <c r="J96" t="n">
-        <v>0.3702343949807545</v>
+        <v>0.2444812382119239</v>
       </c>
       <c r="K96" t="n">
         <v>1</v>
@@ -4288,28 +4300,28 @@
         <v>2001</v>
       </c>
       <c r="C97" t="n">
-        <v>11.17204374620849</v>
+        <v>11.44770457333097</v>
       </c>
       <c r="D97" t="n">
-        <v>4.956126416533477</v>
+        <v>4.848424600170276</v>
       </c>
       <c r="E97" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F97" t="n">
-        <v>12.74720876961259</v>
+        <v>12.74301544364894</v>
       </c>
       <c r="G97" t="n">
-        <v>1.61789618620625</v>
+        <v>1.667599591019885</v>
       </c>
       <c r="H97" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I97" t="n">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="J97" t="n">
-        <v>0.1437546787388434</v>
+        <v>0.2273426481434702</v>
       </c>
       <c r="K97" t="n">
         <v>1</v>
@@ -4328,28 +4340,28 @@
         <v>2002</v>
       </c>
       <c r="C98" t="n">
-        <v>12.33018655112426</v>
+        <v>12.5141170617537</v>
       </c>
       <c r="D98" t="n">
-        <v>4.229338230350741</v>
+        <v>4.285548358147345</v>
       </c>
       <c r="E98" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F98" t="n">
-        <v>11.73406232652511</v>
+        <v>11.76584363813859</v>
       </c>
       <c r="G98" t="n">
-        <v>1.947780237644961</v>
+        <v>2.003445148984976</v>
       </c>
       <c r="H98" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I98" t="n">
-        <v>463</v>
+        <v>434</v>
       </c>
       <c r="J98" t="n">
-        <v>0.9623859426241785</v>
+        <v>0.8002583353165299</v>
       </c>
       <c r="K98" t="n">
         <v>1</v>
@@ -4368,28 +4380,28 @@
         <v>2003</v>
       </c>
       <c r="C99" t="n">
-        <v>12.09465114317047</v>
+        <v>12.17792174605952</v>
       </c>
       <c r="D99" t="n">
-        <v>4.807319713424447</v>
+        <v>4.894256836589344</v>
       </c>
       <c r="E99" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F99" t="n">
-        <v>14.68121271287553</v>
+        <v>15.01856153053471</v>
       </c>
       <c r="G99" t="n">
-        <v>2.803412770463163</v>
+        <v>2.532912658976403</v>
       </c>
       <c r="H99" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I99" t="n">
-        <v>342</v>
+        <v>304</v>
       </c>
       <c r="J99" t="n">
-        <v>0.1164745728462857</v>
+        <v>0.1069504346982763</v>
       </c>
       <c r="K99" t="n">
         <v>1</v>
@@ -4408,28 +4420,28 @@
         <v>2004</v>
       </c>
       <c r="C100" t="n">
-        <v>12.10534895726616</v>
+        <v>12.25100284112239</v>
       </c>
       <c r="D100" t="n">
-        <v>3.199111134439387</v>
+        <v>3.082953831395014</v>
       </c>
       <c r="E100" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F100" t="n">
-        <v>12.64746176374874</v>
+        <v>12.46670225892175</v>
       </c>
       <c r="G100" t="n">
-        <v>1.87750774996869</v>
+        <v>1.786026899207281</v>
       </c>
       <c r="H100" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I100" t="n">
-        <v>435</v>
+        <v>421</v>
       </c>
       <c r="J100" t="n">
-        <v>0.7515139480660298</v>
+        <v>0.9481258860583575</v>
       </c>
       <c r="K100" t="n">
         <v>1</v>
@@ -4448,31 +4460,31 @@
         <v>2005</v>
       </c>
       <c r="C101" t="n">
-        <v>11.97164762386854</v>
+        <v>12.11121575842528</v>
       </c>
       <c r="D101" t="n">
-        <v>3.013633089631853</v>
+        <v>3.033696710298604</v>
       </c>
       <c r="E101" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F101" t="n">
-        <v>13.46717552624691</v>
+        <v>13.4304157853346</v>
       </c>
       <c r="G101" t="n">
-        <v>1.873779156820327</v>
+        <v>1.925491395380593</v>
       </c>
       <c r="H101" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I101" t="n">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="J101" t="n">
-        <v>0.01939897809540304</v>
+        <v>0.03937493907824695</v>
       </c>
       <c r="K101" t="n">
-        <v>0.5819693428620913</v>
+        <v>1</v>
       </c>
       <c r="L101" t="b">
         <v>0</v>
@@ -4488,31 +4500,31 @@
         <v>2006</v>
       </c>
       <c r="C102" t="n">
-        <v>12.1177195445798</v>
+        <v>12.41087928775852</v>
       </c>
       <c r="D102" t="n">
-        <v>4.237608691480863</v>
+        <v>4.221071469416702</v>
       </c>
       <c r="E102" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F102" t="n">
-        <v>16.87160404024931</v>
+        <v>17.17959275680654</v>
       </c>
       <c r="G102" t="n">
-        <v>1.705901501861033</v>
+        <v>1.216310543396789</v>
       </c>
       <c r="H102" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I102" t="n">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="J102" t="n">
-        <v>3.932581683268636e-06</v>
+        <v>2.711033761670014e-06</v>
       </c>
       <c r="K102" t="n">
-        <v>0.0001179774504980591</v>
+        <v>8.133101285010042e-05</v>
       </c>
       <c r="L102" t="b">
         <v>1</v>
@@ -4528,28 +4540,28 @@
         <v>2007</v>
       </c>
       <c r="C103" t="n">
-        <v>13.93867204605621</v>
+        <v>14.12608148305752</v>
       </c>
       <c r="D103" t="n">
-        <v>3.297943493630327</v>
+        <v>3.220062535557557</v>
       </c>
       <c r="E103" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F103" t="n">
-        <v>13.16819452154433</v>
+        <v>13.12927005369341</v>
       </c>
       <c r="G103" t="n">
-        <v>1.520162656748922</v>
+        <v>1.558707306729744</v>
       </c>
       <c r="H103" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I103" t="n">
-        <v>530</v>
+        <v>501</v>
       </c>
       <c r="J103" t="n">
-        <v>0.3421472132719123</v>
+        <v>0.2218247681863602</v>
       </c>
       <c r="K103" t="n">
         <v>1</v>
@@ -4568,28 +4580,28 @@
         <v>2008</v>
       </c>
       <c r="C104" t="n">
-        <v>12.03359808447124</v>
+        <v>12.26042276819608</v>
       </c>
       <c r="D104" t="n">
-        <v>4.512888641420473</v>
+        <v>4.455686890498154</v>
       </c>
       <c r="E104" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F104" t="n">
-        <v>10.71637283615037</v>
+        <v>10.88275741674798</v>
       </c>
       <c r="G104" t="n">
-        <v>1.04921958795249</v>
+        <v>0.8360864282454312</v>
       </c>
       <c r="H104" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I104" t="n">
-        <v>512</v>
+        <v>472</v>
       </c>
       <c r="J104" t="n">
-        <v>0.4793206872507</v>
+        <v>0.422314692328384</v>
       </c>
       <c r="K104" t="n">
         <v>1</v>
@@ -4608,28 +4620,28 @@
         <v>2009</v>
       </c>
       <c r="C105" t="n">
-        <v>14.25838576129004</v>
+        <v>14.54154620057235</v>
       </c>
       <c r="D105" t="n">
-        <v>3.14521112686733</v>
+        <v>2.638729403336222</v>
       </c>
       <c r="E105" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F105" t="n">
-        <v>15.06694454547191</v>
+        <v>15.28074187818632</v>
       </c>
       <c r="G105" t="n">
-        <v>2.544288742097876</v>
+        <v>2.470007072312821</v>
       </c>
       <c r="H105" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I105" t="n">
-        <v>382</v>
+        <v>333</v>
       </c>
       <c r="J105" t="n">
-        <v>0.3026456847671452</v>
+        <v>0.2329576809460173</v>
       </c>
       <c r="K105" t="n">
         <v>1</v>
@@ -4648,28 +4660,28 @@
         <v>2010</v>
       </c>
       <c r="C106" t="n">
-        <v>10.82854260323885</v>
+        <v>10.93290831226477</v>
       </c>
       <c r="D106" t="n">
-        <v>2.616364816757962</v>
+        <v>2.733850026978311</v>
       </c>
       <c r="E106" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F106" t="n">
-        <v>12.20188134479301</v>
+        <v>12.20615746013664</v>
       </c>
       <c r="G106" t="n">
-        <v>2.418013514587452</v>
+        <v>2.492368922082301</v>
       </c>
       <c r="H106" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I106" t="n">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="J106" t="n">
-        <v>0.06788728165286495</v>
+        <v>0.1008039293797245</v>
       </c>
       <c r="K106" t="n">
         <v>1</v>
@@ -4688,31 +4700,31 @@
         <v>2011</v>
       </c>
       <c r="C107" t="n">
-        <v>13.75837431150639</v>
+        <v>13.95851606631785</v>
       </c>
       <c r="D107" t="n">
-        <v>3.493304104131062</v>
+        <v>3.427836439740505</v>
       </c>
       <c r="E107" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F107" t="n">
-        <v>16.10899006527436</v>
+        <v>16.08159575333546</v>
       </c>
       <c r="G107" t="n">
-        <v>1.326956867425245</v>
+        <v>1.363124284302486</v>
       </c>
       <c r="H107" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I107" t="n">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="J107" t="n">
-        <v>0.003687926511788826</v>
+        <v>0.007977520283345307</v>
       </c>
       <c r="K107" t="n">
-        <v>0.1106377953536648</v>
+        <v>0.2393256085003592</v>
       </c>
       <c r="L107" t="b">
         <v>0</v>
@@ -4728,28 +4740,28 @@
         <v>2012</v>
       </c>
       <c r="C108" t="n">
-        <v>12.18001540698956</v>
+        <v>12.36831491401533</v>
       </c>
       <c r="D108" t="n">
-        <v>4.974505209289701</v>
+        <v>5.050314508161486</v>
       </c>
       <c r="E108" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F108" t="n">
-        <v>13.53117251456386</v>
+        <v>13.67318411704084</v>
       </c>
       <c r="G108" t="n">
-        <v>1.583813030241731</v>
+        <v>1.523941822343905</v>
       </c>
       <c r="H108" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I108" t="n">
-        <v>338</v>
+        <v>309</v>
       </c>
       <c r="J108" t="n">
-        <v>0.1044523925839264</v>
+        <v>0.1236180104465049</v>
       </c>
       <c r="K108" t="n">
         <v>1</v>
@@ -4768,28 +4780,28 @@
         <v>2013</v>
       </c>
       <c r="C109" t="n">
-        <v>11.18423093611017</v>
+        <v>11.53682059208821</v>
       </c>
       <c r="D109" t="n">
-        <v>6.090850813719808</v>
+        <v>5.779508232411917</v>
       </c>
       <c r="E109" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F109" t="n">
-        <v>11.28393726511102</v>
+        <v>11.38997722095669</v>
       </c>
       <c r="G109" t="n">
-        <v>1.73346762500044</v>
+        <v>1.732501328816145</v>
       </c>
       <c r="H109" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I109" t="n">
-        <v>540</v>
+        <v>497</v>
       </c>
       <c r="J109" t="n">
-        <v>0.278066416419971</v>
+        <v>0.2444812382119239</v>
       </c>
       <c r="K109" t="n">
         <v>1</v>
@@ -4808,31 +4820,31 @@
         <v>2014</v>
       </c>
       <c r="C110" t="n">
-        <v>12.96031404546967</v>
+        <v>13.06480637813208</v>
       </c>
       <c r="D110" t="n">
-        <v>2.963161991258624</v>
+        <v>3.049663327732754</v>
       </c>
       <c r="E110" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F110" t="n">
-        <v>15.03261167792853</v>
+        <v>15.16509552283323</v>
       </c>
       <c r="G110" t="n">
-        <v>2.276295318341627</v>
+        <v>2.28188122479908</v>
       </c>
       <c r="H110" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I110" t="n">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="J110" t="n">
-        <v>0.007185918907506455</v>
+        <v>0.007642297798458144</v>
       </c>
       <c r="K110" t="n">
-        <v>0.2155775672251936</v>
+        <v>0.2292689339537443</v>
       </c>
       <c r="L110" t="b">
         <v>0</v>
@@ -4848,28 +4860,28 @@
         <v>2015</v>
       </c>
       <c r="C111" t="n">
-        <v>12.12523793453934</v>
+        <v>12.35744595192199</v>
       </c>
       <c r="D111" t="n">
-        <v>4.190480231683097</v>
+        <v>4.157499001494224</v>
       </c>
       <c r="E111" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F111" t="n">
-        <v>13.3032965805912</v>
+        <v>13.24137819991319</v>
       </c>
       <c r="G111" t="n">
-        <v>1.499607266195056</v>
+        <v>1.524531818348895</v>
       </c>
       <c r="H111" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I111" t="n">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="J111" t="n">
-        <v>0.6810995611770312</v>
+        <v>0.9251280814116045</v>
       </c>
       <c r="K111" t="n">
         <v>1</v>
@@ -4888,31 +4900,31 @@
         <v>2016</v>
       </c>
       <c r="C112" t="n">
-        <v>11.9790026033192</v>
+        <v>12.19971985114351</v>
       </c>
       <c r="D112" t="n">
-        <v>3.564957094300757</v>
+        <v>3.597034895910502</v>
       </c>
       <c r="E112" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F112" t="n">
-        <v>15.37908762593872</v>
+        <v>15.79159819394724</v>
       </c>
       <c r="G112" t="n">
-        <v>1.987197715549046</v>
+        <v>1.141472717592461</v>
       </c>
       <c r="H112" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I112" t="n">
-        <v>217</v>
+        <v>172</v>
       </c>
       <c r="J112" t="n">
-        <v>0.001137844145906955</v>
+        <v>0.0004307467455584698</v>
       </c>
       <c r="K112" t="n">
-        <v>0.03413532437720863</v>
+        <v>0.01292240236675409</v>
       </c>
       <c r="L112" t="b">
         <v>1</v>
@@ -4928,31 +4940,31 @@
         <v>2017</v>
       </c>
       <c r="C113" t="n">
-        <v>11.80163601338617</v>
+        <v>11.84111721611719</v>
       </c>
       <c r="D113" t="n">
-        <v>4.182731514142461</v>
+        <v>4.30238587247992</v>
       </c>
       <c r="E113" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F113" t="n">
-        <v>13.66716723135718</v>
+        <v>13.86598193947277</v>
       </c>
       <c r="G113" t="n">
-        <v>1.322167414504114</v>
+        <v>1.088770265116808</v>
       </c>
       <c r="H113" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I113" t="n">
-        <v>270</v>
+        <v>242</v>
       </c>
       <c r="J113" t="n">
-        <v>0.0110888301519186</v>
+        <v>0.01212652114663073</v>
       </c>
       <c r="K113" t="n">
-        <v>0.3326649045575581</v>
+        <v>0.3637956343989219</v>
       </c>
       <c r="L113" t="b">
         <v>0</v>
@@ -4968,28 +4980,28 @@
         <v>2018</v>
       </c>
       <c r="C114" t="n">
-        <v>15.2933205577852</v>
+        <v>15.69369237444404</v>
       </c>
       <c r="D114" t="n">
-        <v>4.202825803835061</v>
+        <v>3.867288122078625</v>
       </c>
       <c r="E114" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F114" t="n">
-        <v>13.8023369256586</v>
+        <v>13.85199791192099</v>
       </c>
       <c r="G114" t="n">
-        <v>4.073924262035966</v>
+        <v>4.194310067596842</v>
       </c>
       <c r="H114" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I114" t="n">
-        <v>579</v>
+        <v>539</v>
       </c>
       <c r="J114" t="n">
-        <v>0.1073613890542134</v>
+        <v>0.07654582326360251</v>
       </c>
       <c r="K114" t="n">
         <v>1</v>
@@ -5008,31 +5020,31 @@
         <v>2019</v>
       </c>
       <c r="C115" t="n">
-        <v>12.14555617826304</v>
+        <v>12.13839468238666</v>
       </c>
       <c r="D115" t="n">
-        <v>3.032078039935536</v>
+        <v>2.958731106120998</v>
       </c>
       <c r="E115" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F115" t="n">
-        <v>13.72844094357556</v>
+        <v>14.03445059117036</v>
       </c>
       <c r="G115" t="n">
-        <v>2.140386835534156</v>
+        <v>1.809881741558641</v>
       </c>
       <c r="H115" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I115" t="n">
-        <v>289</v>
+        <v>232</v>
       </c>
       <c r="J115" t="n">
-        <v>0.02237875272121164</v>
+        <v>0.007977520283345307</v>
       </c>
       <c r="K115" t="n">
-        <v>0.6713625816363492</v>
+        <v>0.2393256085003592</v>
       </c>
       <c r="L115" t="b">
         <v>0</v>
@@ -5048,31 +5060,31 @@
         <v>2020</v>
       </c>
       <c r="C116" t="n">
-        <v>12.64553126996176</v>
+        <v>12.9435494839253</v>
       </c>
       <c r="D116" t="n">
-        <v>3.608068472601522</v>
+        <v>3.296535729303976</v>
       </c>
       <c r="E116" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F116" t="n">
-        <v>14.92399456365685</v>
+        <v>15.08115474834576</v>
       </c>
       <c r="G116" t="n">
-        <v>2.665800142917662</v>
+        <v>2.670347833153741</v>
       </c>
       <c r="H116" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I116" t="n">
-        <v>294</v>
+        <v>260</v>
       </c>
       <c r="J116" t="n">
-        <v>0.02665685861087328</v>
+        <v>0.02456348443163473</v>
       </c>
       <c r="K116" t="n">
-        <v>0.7997057583261985</v>
+        <v>0.736904532949042</v>
       </c>
       <c r="L116" t="b">
         <v>0</v>
@@ -5088,31 +5100,31 @@
         <v>2021</v>
       </c>
       <c r="C117" t="n">
-        <v>10.25731741612528</v>
+        <v>10.21837363471757</v>
       </c>
       <c r="D117" t="n">
-        <v>3.819965974250919</v>
+        <v>3.876904161918121</v>
       </c>
       <c r="E117" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F117" t="n">
-        <v>14.93686440407594</v>
+        <v>14.98520074031887</v>
       </c>
       <c r="G117" t="n">
-        <v>1.703332743525768</v>
+        <v>1.744407496412848</v>
       </c>
       <c r="H117" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I117" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="J117" t="n">
-        <v>2.656183265955209e-06</v>
+        <v>5.827773072653603e-06</v>
       </c>
       <c r="K117" t="n">
-        <v>7.968549797865627e-05</v>
+        <v>0.0001748331921796081</v>
       </c>
       <c r="L117" t="b">
         <v>1</v>
@@ -5128,28 +5140,28 @@
         <v>2022</v>
       </c>
       <c r="C118" t="n">
-        <v>12.96541463854332</v>
+        <v>13.14209167117357</v>
       </c>
       <c r="D118" t="n">
-        <v>5.464186180024499</v>
+        <v>5.517259299016072</v>
       </c>
       <c r="E118" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F118" t="n">
-        <v>11.86155568988001</v>
+        <v>11.77480022985392</v>
       </c>
       <c r="G118" t="n">
-        <v>1.384544954704631</v>
+        <v>1.381602099002886</v>
       </c>
       <c r="H118" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I118" t="n">
-        <v>493</v>
+        <v>465</v>
       </c>
       <c r="J118" t="n">
-        <v>0.6517115543521071</v>
+        <v>0.483173932450471</v>
       </c>
       <c r="K118" t="n">
         <v>1</v>
@@ -5168,31 +5180,31 @@
         <v>2023</v>
       </c>
       <c r="C119" t="n">
-        <v>11.58188189812308</v>
+        <v>11.7821376419686</v>
       </c>
       <c r="D119" t="n">
-        <v>3.927157043379661</v>
+        <v>3.971899123215706</v>
       </c>
       <c r="E119" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F119" t="n">
-        <v>17.94051665447138</v>
+        <v>18.20465183883177</v>
       </c>
       <c r="G119" t="n">
-        <v>1.916662260292925</v>
+        <v>1.648377424406352</v>
       </c>
       <c r="H119" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I119" t="n">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="J119" t="n">
-        <v>1.326476570808314e-07</v>
+        <v>1.165594868674933e-07</v>
       </c>
       <c r="K119" t="n">
-        <v>3.979429712424942e-06</v>
+        <v>3.496784606024798e-06</v>
       </c>
       <c r="L119" t="b">
         <v>1</v>
@@ -5208,28 +5220,28 @@
         <v>2024</v>
       </c>
       <c r="C120" t="n">
-        <v>14.74219047332889</v>
+        <v>14.84775460748009</v>
       </c>
       <c r="D120" t="n">
-        <v>4.349295874244592</v>
+        <v>4.331956249870275</v>
       </c>
       <c r="E120" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F120" t="n">
-        <v>14.48165844812772</v>
+        <v>14.75387979989179</v>
       </c>
       <c r="G120" t="n">
-        <v>2.815830660349234</v>
+        <v>2.676692512774226</v>
       </c>
       <c r="H120" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I120" t="n">
-        <v>517</v>
+        <v>468</v>
       </c>
       <c r="J120" t="n">
-        <v>0.4384776005917429</v>
+        <v>0.4565253750516055</v>
       </c>
       <c r="K120" t="n">
         <v>1</v>
@@ -5248,28 +5260,28 @@
         <v>2025</v>
       </c>
       <c r="C121" t="n">
-        <v>14.03030747350917</v>
+        <v>14.18783344427337</v>
       </c>
       <c r="D121" t="n">
-        <v>3.534317039682366</v>
+        <v>3.350346156369826</v>
       </c>
       <c r="E121" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F121" t="n">
-        <v>13.52565997518527</v>
+        <v>13.77961972687935</v>
       </c>
       <c r="G121" t="n">
-        <v>3.500688553207163</v>
+        <v>3.453161185789998</v>
       </c>
       <c r="H121" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I121" t="n">
-        <v>532</v>
+        <v>484</v>
       </c>
       <c r="J121" t="n">
-        <v>0.3286287619001479</v>
+        <v>0.3291108266514761</v>
       </c>
       <c r="K121" t="n">
         <v>1</v>
